--- a/SilniczkiExcel.xlsx
+++ b/SilniczkiExcel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\tech\robotyka\robots\evangelion-turbo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C32340E-C491-453E-9D71-F9DF8B18EB89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B222485A-06DA-40D6-93BA-7D8521B89717}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="480" windowWidth="38640" windowHeight="21240" xr2:uid="{511008C5-3BC9-4B59-854A-53C66BDAD283}"/>
+    <workbookView xWindow="-120" yWindow="480" windowWidth="29040" windowHeight="15840" xr2:uid="{511008C5-3BC9-4B59-854A-53C66BDAD283}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t>Nazwa</t>
   </si>
@@ -80,28 +80,13 @@
     <t>Opór uzwojeń [U/1A]</t>
   </si>
   <si>
-    <t>Stała momentu [Nm/mA]</t>
-  </si>
-  <si>
-    <t>Moment w zwarciu 12V [Nm/A]</t>
-  </si>
-  <si>
     <t>Prąd w zwarciu 12V [A]</t>
-  </si>
-  <si>
-    <t>RPM 24V</t>
-  </si>
-  <si>
-    <t>Prąd 24V [mA]</t>
   </si>
   <si>
     <t>Prąd w zwarciu (Dane U)</t>
   </si>
   <si>
     <t>RPM (Dane U)</t>
-  </si>
-  <si>
-    <t>Moment [Nm/A] (Dane U)</t>
   </si>
   <si>
     <t>[Nm/g] (Dane U)</t>
@@ -120,6 +105,24 @@
   </si>
   <si>
     <t>RS-360ST-2885</t>
+  </si>
+  <si>
+    <t>pololu 37d HP 12v</t>
+  </si>
+  <si>
+    <t>Moment [Nm] (Dane U)</t>
+  </si>
+  <si>
+    <t>Prąd 12V [mA]</t>
+  </si>
+  <si>
+    <t>RPM 12V</t>
+  </si>
+  <si>
+    <t>Stała momentu [mNm/A]</t>
+  </si>
+  <si>
+    <t>Moment w zwarciu 12V [mNm]</t>
   </si>
 </sst>
 </file>
@@ -417,15 +420,9 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -435,11 +432,39 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="23">
+  <dxfs count="24">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.749961851863155"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.749961851863155"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -817,6 +842,22 @@
       </border>
     </dxf>
     <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <border>
         <bottom style="thin">
           <color indexed="64"/>
@@ -831,22 +872,6 @@
         <right style="thin">
           <color indexed="64"/>
         </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
         <top/>
         <bottom/>
         <vertical style="thin">
@@ -856,17 +881,6 @@
           <color indexed="64"/>
         </horizontal>
       </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.749961851863155"/>
-        </patternFill>
-      </fill>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -882,46 +896,46 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{AC265550-FF17-485F-9292-5B99975F35F1}" name="Table6" displayName="Table6" ref="A1:P1048576" totalsRowShown="0" headerRowDxfId="21" headerRowBorderDxfId="19" tableBorderDxfId="20" totalsRowBorderDxfId="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{AC265550-FF17-485F-9292-5B99975F35F1}" name="Table6" displayName="Table6" ref="A1:P1048576" totalsRowShown="0" headerRowDxfId="23" headerRowBorderDxfId="22" tableBorderDxfId="21" totalsRowBorderDxfId="20">
   <autoFilter ref="A1:P1048576" xr:uid="{AC265550-FF17-485F-9292-5B99975F35F1}"/>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{F9A7EC63-1D4A-4C94-8631-E9F11B91398D}" name="Nazwa" dataDxfId="17"/>
-    <tableColumn id="2" xr3:uid="{276B8804-5769-4B88-907D-9FC75BD252C8}" name="Waga" dataDxfId="16"/>
-    <tableColumn id="4" xr3:uid="{F4A061AF-E573-4F92-8E59-AEC883A58204}" name="Opór uzwojeń [U/1A]" dataDxfId="15"/>
-    <tableColumn id="5" xr3:uid="{A44E980B-70F8-4B74-AF97-3C900A21C351}" name="RPM 24V" dataDxfId="14"/>
-    <tableColumn id="6" xr3:uid="{776A220E-593B-4B22-AB1F-214C9A436F19}" name="Prąd 24V [mA]" dataDxfId="13"/>
-    <tableColumn id="7" xr3:uid="{199A7165-012B-4850-A0FE-5761864209B2}" name="Stała momentu [Nm/mA]" dataDxfId="12">
-      <calculatedColumnFormula>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</calculatedColumnFormula>
+    <tableColumn id="1" xr3:uid="{F9A7EC63-1D4A-4C94-8631-E9F11B91398D}" name="Nazwa" dataDxfId="19"/>
+    <tableColumn id="2" xr3:uid="{276B8804-5769-4B88-907D-9FC75BD252C8}" name="Waga" dataDxfId="18"/>
+    <tableColumn id="4" xr3:uid="{F4A061AF-E573-4F92-8E59-AEC883A58204}" name="Opór uzwojeń [U/1A]" dataDxfId="17"/>
+    <tableColumn id="5" xr3:uid="{A44E980B-70F8-4B74-AF97-3C900A21C351}" name="RPM 12V" dataDxfId="16"/>
+    <tableColumn id="6" xr3:uid="{776A220E-593B-4B22-AB1F-214C9A436F19}" name="Prąd 12V [mA]" dataDxfId="15"/>
+    <tableColumn id="7" xr3:uid="{199A7165-012B-4850-A0FE-5761864209B2}" name="Stała momentu [mNm/A]" dataDxfId="14">
+      <calculatedColumnFormula>(12-Table6[[#This Row],[Prąd 12V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{55F3429F-8468-494B-B971-71BCE955500A}" name="Prąd w zwarciu 12V [A]" dataDxfId="11">
+    <tableColumn id="17" xr3:uid="{55F3429F-8468-494B-B971-71BCE955500A}" name="Prąd w zwarciu 12V [A]" dataDxfId="13">
       <calculatedColumnFormula>12/Table6[[#This Row],[Opór uzwojeń '[U/1A']]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{7EFBC617-C9B9-4B2D-8DC9-69B3B4A9327E}" name="Moment w zwarciu 12V [Nm/A]" dataDxfId="10">
-      <calculatedColumnFormula>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</calculatedColumnFormula>
+    <tableColumn id="18" xr3:uid="{7EFBC617-C9B9-4B2D-8DC9-69B3B4A9327E}" name="Moment w zwarciu 12V [mNm]" dataDxfId="12">
+      <calculatedColumnFormula>Table6[[#This Row],[Stała momentu '[mNm/A']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 12V '[mA']]]/1000)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{69CD1EDF-51AC-407C-9E31-80182F0F74C6}" name="Napięcie (Dane RPM)" dataDxfId="9">
-      <calculatedColumnFormula>$S$2*24/Table6[[#This Row],[RPM 24V]]</calculatedColumnFormula>
+    <tableColumn id="8" xr3:uid="{69CD1EDF-51AC-407C-9E31-80182F0F74C6}" name="Napięcie (Dane RPM)" dataDxfId="11">
+      <calculatedColumnFormula>$S$2*24/Table6[[#This Row],[RPM 12V]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{68200736-7943-41FD-A9E9-CE88B52BBDBE}" name="Prąd w zwarciu (Dane RPM)" dataDxfId="8">
+    <tableColumn id="10" xr3:uid="{68200736-7943-41FD-A9E9-CE88B52BBDBE}" name="Prąd w zwarciu (Dane RPM)" dataDxfId="10">
       <calculatedColumnFormula>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{4295B029-6DEF-402F-8CEA-5C0420380648}" name="Moment (Dane RPM)" dataDxfId="7">
-      <calculatedColumnFormula>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</calculatedColumnFormula>
+    <tableColumn id="11" xr3:uid="{4295B029-6DEF-402F-8CEA-5C0420380648}" name="Moment (Dane RPM)" dataDxfId="9">
+      <calculatedColumnFormula>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{9518D69E-613C-4364-BA73-1234317D9EAB}" name="[Nm/g] (Dane RPM)" dataDxfId="6">
-      <calculatedColumnFormula>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</calculatedColumnFormula>
+    <tableColumn id="12" xr3:uid="{9518D69E-613C-4364-BA73-1234317D9EAB}" name="[Nm/g] (Dane RPM)" dataDxfId="8">
+      <calculatedColumnFormula>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{458715B8-2553-4AFB-BD1A-63EFEC89C3AF}" name="RPM (Dane U)" dataDxfId="5">
-      <calculatedColumnFormula>Table6[[#This Row],[RPM 24V]]*$S$3/24</calculatedColumnFormula>
+    <tableColumn id="13" xr3:uid="{458715B8-2553-4AFB-BD1A-63EFEC89C3AF}" name="RPM (Dane U)" dataDxfId="7">
+      <calculatedColumnFormula>Table6[[#This Row],[RPM 12V]]*$S$3/24</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{E50BDF0E-1B89-4839-B5C1-10C416C379A0}" name="Prąd w zwarciu (Dane U)" dataDxfId="4">
+    <tableColumn id="15" xr3:uid="{E50BDF0E-1B89-4839-B5C1-10C416C379A0}" name="Prąd w zwarciu (Dane U)" dataDxfId="6">
       <calculatedColumnFormula>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{8C6AAA0F-FBFF-4B85-A456-65D77F8FF3CF}" name="Moment [Nm/A] (Dane U)" dataDxfId="3">
-      <calculatedColumnFormula>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</calculatedColumnFormula>
+    <tableColumn id="19" xr3:uid="{8C6AAA0F-FBFF-4B85-A456-65D77F8FF3CF}" name="Moment [Nm] (Dane U)" dataDxfId="5">
+      <calculatedColumnFormula>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{DD076DF6-AE6B-40EE-84ED-FD4D6650BC91}" name="[Nm/g] (Dane U)" dataDxfId="2">
-      <calculatedColumnFormula>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</calculatedColumnFormula>
+    <tableColumn id="16" xr3:uid="{DD076DF6-AE6B-40EE-84ED-FD4D6650BC91}" name="[Nm/g] (Dane U)" dataDxfId="4">
+      <calculatedColumnFormula>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1262,7 +1276,7 @@
     <col min="12" max="12" width="20" style="5" customWidth="1"/>
     <col min="13" max="13" width="16" style="3" customWidth="1"/>
     <col min="14" max="14" width="24.140625" style="4" customWidth="1"/>
-    <col min="15" max="15" width="25" style="7" customWidth="1"/>
+    <col min="15" max="15" width="28.42578125" style="7" customWidth="1"/>
     <col min="16" max="16" width="17.85546875" style="5" customWidth="1"/>
     <col min="17" max="17" width="6.28515625" customWidth="1"/>
     <col min="18" max="18" width="27.42578125" customWidth="1"/>
@@ -1279,19 +1293,19 @@
         <v>13</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="E1" s="12" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="F1" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="G1" s="10" t="s">
-        <v>16</v>
-      </c>
       <c r="H1" s="11" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="I1" s="9" t="s">
         <v>8</v>
@@ -1303,24 +1317,24 @@
         <v>10</v>
       </c>
       <c r="L1" s="11" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M1" s="9" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="N1" s="10" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="O1" s="12" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="P1" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="R1" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="R1" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="S1" s="14"/>
+      <c r="S1" s="20"/>
     </row>
     <row r="2" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
@@ -1333,59 +1347,59 @@
         <v>2</v>
       </c>
       <c r="D2" s="4">
-        <v>22000</v>
+        <v>10000</v>
       </c>
       <c r="E2" s="7">
-        <v>245</v>
+        <v>123</v>
       </c>
       <c r="F2" s="3">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
-        <v>5.1874383406124771</v>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
+        <v>11.224243206612826</v>
       </c>
       <c r="G2" s="4">
         <f>12/Table6[[#This Row],[Opór uzwojeń '[U/1A']]]</f>
         <v>6</v>
       </c>
       <c r="H2" s="5">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
-        <v>29.853707650224806</v>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
+        <v>67.345459239676956</v>
       </c>
       <c r="I2" s="3">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
-        <v>10.909090909090908</v>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>24</v>
       </c>
       <c r="J2" s="4">
         <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>5.4545454545454541</v>
+        <v>12</v>
       </c>
       <c r="K2" s="4">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>27.139734227477092</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>134.69091847935391</v>
       </c>
       <c r="L2" s="5">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>0.36042143728389237</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <v>1.7887240169900918</v>
       </c>
       <c r="M2" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
-        <v>7333.333333333333</v>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>5000</v>
       </c>
       <c r="N2" s="4">
         <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O2" s="7">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
-        <v>19.902471766816536</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <v>67.345459239676956</v>
       </c>
       <c r="P2" s="5">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
-        <v>0.26430905400818772</v>
-      </c>
-      <c r="R2" s="16" t="s">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>0.89436200849504588</v>
+      </c>
+      <c r="R2" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="S2" s="19">
+      <c r="S2" s="17">
         <v>10000</v>
       </c>
     </row>
@@ -1400,60 +1414,60 @@
         <v>3.85</v>
       </c>
       <c r="D3" s="4">
-        <v>20800</v>
+        <v>10000</v>
       </c>
       <c r="E3" s="7">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F3" s="3">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
-        <v>5.4738588071673124</v>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
+        <v>11.091507984074187</v>
       </c>
       <c r="G3" s="4">
         <f>12/Table6[[#This Row],[Opór uzwojeń '[U/1A']]]</f>
         <v>3.116883116883117</v>
       </c>
       <c r="H3" s="5">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
-        <v>15.96660633882829</v>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
+        <v>34.570933976335134</v>
       </c>
       <c r="I3" s="3">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
-        <v>11.538461538461538</v>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>24</v>
       </c>
       <c r="J3" s="4">
         <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>2.9970029970029972</v>
+        <v>6.233766233766235</v>
       </c>
       <c r="K3" s="4">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>15.352506095027202</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>69.141867952670268</v>
       </c>
       <c r="L3" s="5">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>0.2171500154883621</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <v>0.97796135718062605</v>
       </c>
       <c r="M3" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
-        <v>6933.333333333333</v>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>5000</v>
       </c>
       <c r="N3" s="4">
         <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>2.0779220779220782</v>
+        <v>3.1168831168831175</v>
       </c>
       <c r="O3" s="7">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
-        <v>10.644404225885527</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <v>34.570933976335134</v>
       </c>
       <c r="P3" s="5">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
-        <v>0.15055734407193105</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>0.48898067859031302</v>
       </c>
       <c r="R3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="S3" s="20">
-        <v>8</v>
+      <c r="S3" s="18">
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -1467,59 +1481,59 @@
         <v>2.0499999999999998</v>
       </c>
       <c r="D4" s="4">
-        <v>24800</v>
+        <v>10000</v>
       </c>
       <c r="E4" s="7">
-        <v>225</v>
+        <v>113</v>
       </c>
       <c r="F4" s="3">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
-        <v>4.6028668435950735</v>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
+        <v>11.237946447213039</v>
       </c>
       <c r="G4" s="4">
         <f>12/Table6[[#This Row],[Opór uzwojeń '[U/1A']]]</f>
         <v>5.8536585365853666</v>
       </c>
       <c r="H4" s="5">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
-        <v>25.907965751967154</v>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
+        <v>65.783101154417793</v>
       </c>
       <c r="I4" s="3">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
-        <v>9.67741935483871</v>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>24</v>
       </c>
       <c r="J4" s="4">
         <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>4.7206923682140056</v>
+        <v>11.707317073170733</v>
       </c>
       <c r="K4" s="4">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>20.893520767715447</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>131.56620230883559</v>
       </c>
       <c r="L4" s="5">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>0.30019426390395759</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <v>1.8903189986901665</v>
       </c>
       <c r="M4" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
-        <v>8266.6666666666661</v>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>5000</v>
       </c>
       <c r="N4" s="4">
         <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>3.9024390243902443</v>
+        <v>5.8536585365853666</v>
       </c>
       <c r="O4" s="7">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
-        <v>17.271977167978104</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <v>65.783101154417793</v>
       </c>
       <c r="P4" s="5">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
-        <v>0.24816059149393829</v>
-      </c>
-      <c r="R4" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="S4" s="19">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>0.94515949934508325</v>
+      </c>
+      <c r="R4" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="S4" s="17">
         <v>30</v>
       </c>
     </row>
@@ -1534,59 +1548,59 @@
         <v>2.5</v>
       </c>
       <c r="D5" s="4">
-        <v>23000</v>
+        <v>10000</v>
       </c>
       <c r="E5" s="7">
-        <v>255</v>
+        <v>123</v>
       </c>
       <c r="F5" s="3">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
-        <v>4.9557735377755705</v>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
+        <v>11.165515032611918</v>
       </c>
       <c r="G5" s="4">
         <f>12/Table6[[#This Row],[Opór uzwojeń '[U/1A']]]</f>
         <v>4.8</v>
       </c>
       <c r="H5" s="5">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
-        <v>22.523990729189968</v>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
+        <v>53.594472156537201</v>
       </c>
       <c r="I5" s="3">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
-        <v>10.434782608695652</v>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>24</v>
       </c>
       <c r="J5" s="4">
         <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>4.1739130434782608</v>
+        <v>9.6</v>
       </c>
       <c r="K5" s="4">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>19.5860788949478</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>107.1889443130744</v>
       </c>
       <c r="L5" s="5">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>0.27278661413576322</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <v>1.4928822327726241</v>
       </c>
       <c r="M5" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
-        <v>7666.666666666667</v>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>5000</v>
       </c>
       <c r="N5" s="4">
         <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>3.1999999999999997</v>
+        <v>4.8</v>
       </c>
       <c r="O5" s="7">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
-        <v>15.015993819459979</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <v>53.594472156537201</v>
       </c>
       <c r="P5" s="5">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
-        <v>0.2091364041707518</v>
-      </c>
-      <c r="R5" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="S5" s="18">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>0.74644111638631205</v>
+      </c>
+      <c r="R5" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="S5" s="16">
         <v>7.5</v>
       </c>
     </row>
@@ -1601,66 +1615,66 @@
         <v>3.86</v>
       </c>
       <c r="D6" s="4">
-        <v>20745</v>
+        <v>10000</v>
       </c>
       <c r="E6" s="7">
-        <v>220</v>
+        <v>110</v>
       </c>
       <c r="F6" s="3">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
-        <v>5.4847256090683443</v>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
+        <v>11.053692769595553</v>
       </c>
       <c r="G6" s="4">
         <f>12/Table6[[#This Row],[Opór uzwojeń '[U/1A']]]</f>
         <v>3.1088082901554404</v>
       </c>
       <c r="H6" s="5">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
-        <v>15.844320808704479</v>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
+        <v>34.363811718949904</v>
       </c>
       <c r="I6" s="3">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
-        <v>11.569052783803325</v>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>24</v>
       </c>
       <c r="J6" s="4">
         <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>2.9971639336278044</v>
+        <v>6.2176165803108807</v>
       </c>
       <c r="K6" s="4">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>15.275315313284628</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>68.727623437899808</v>
       </c>
       <c r="L6" s="5">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>0.20232205712959772</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <v>0.91029964818410347</v>
       </c>
       <c r="M6" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
-        <v>6915</v>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>5000</v>
       </c>
       <c r="N6" s="4">
         <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>2.0725388601036268</v>
+        <v>3.1088082901554404</v>
       </c>
       <c r="O6" s="7">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
-        <v>10.562880539136319</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <v>34.363811718949904</v>
       </c>
       <c r="P6" s="5">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
-        <v>0.1399057025051168</v>
-      </c>
-      <c r="R6" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="S6" s="18">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>0.45514982409205174</v>
+      </c>
+      <c r="R6" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="S6" s="16">
         <f>S2*S4*PI()/(S5*60000)</f>
         <v>2.0943951023931953</v>
       </c>
     </row>
     <row r="7" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B7" s="7">
         <v>54</v>
@@ -1669,105 +1683,120 @@
         <v>1.5</v>
       </c>
       <c r="D7" s="4">
-        <v>40000</v>
+        <v>20000</v>
       </c>
       <c r="E7" s="7">
-        <v>520</v>
+        <v>260</v>
       </c>
       <c r="F7" s="3">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
-        <v>2.8461678473123646</v>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
+        <v>5.5433666678907141</v>
       </c>
       <c r="G7" s="4">
         <f>12/Table6[[#This Row],[Opór uzwojeń '[U/1A']]]</f>
         <v>8</v>
       </c>
       <c r="H7" s="5">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
-        <v>21.289335497896488</v>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
+        <v>44.346933343125713</v>
       </c>
       <c r="I7" s="3">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
-        <v>6</v>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>12</v>
       </c>
       <c r="J7" s="4">
         <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K7" s="4">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>10.644667748948244</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>44.346933343125706</v>
       </c>
       <c r="L7" s="5">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>0.19712347683237488</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <v>0.82123950635417975</v>
       </c>
       <c r="M7" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
-        <v>13333.333333333334</v>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>10000</v>
       </c>
       <c r="N7" s="4">
         <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>5.333333333333333</v>
+        <v>8</v>
       </c>
       <c r="O7" s="7">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
-        <v>14.192890331930991</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <v>44.346933343125706</v>
       </c>
       <c r="P7" s="5">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
-        <v>0.26283130244316649</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>0.82123950635417975</v>
       </c>
     </row>
     <row r="8" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F8" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G8" s="4" t="e">
-        <f>12/Table6[[#This Row],[Opór uzwojeń '[U/1A']]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H8" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I8" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J8" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K8" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L8" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
+      <c r="A8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="7">
+        <v>109.5</v>
+      </c>
+      <c r="C8" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="D8" s="4">
+        <v>10000</v>
+      </c>
+      <c r="E8" s="7">
+        <v>200</v>
+      </c>
+      <c r="F8" s="3">
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
+        <v>10.848000921143585</v>
+      </c>
+      <c r="G8" s="4">
+        <f>12/Table6[[#This Row],[Opór uzwojeń '[U/1A']]]</f>
+        <v>3.75</v>
+      </c>
+      <c r="H8" s="5">
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
+        <v>40.680003454288446</v>
+      </c>
+      <c r="I8" s="3">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>24</v>
+      </c>
+      <c r="J8" s="4">
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>7.5</v>
+      </c>
+      <c r="K8" s="4">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>81.360006908576892</v>
+      </c>
+      <c r="L8" s="5">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <v>0.74301376172216338</v>
       </c>
       <c r="M8" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
-        <v>0</v>
-      </c>
-      <c r="N8" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O8" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P8" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>5000</v>
+      </c>
+      <c r="N8" s="4">
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>3.75</v>
+      </c>
+      <c r="O8" s="7">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <v>40.680003454288446</v>
+      </c>
+      <c r="P8" s="5">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>0.37150688086108169</v>
       </c>
     </row>
     <row r="9" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F9" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G9" s="4" t="e">
@@ -1775,11 +1804,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H9" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I9" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J9" s="4" t="e">
@@ -1787,15 +1816,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K9" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L9" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M9" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N9" s="4" t="e">
@@ -1803,17 +1832,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O9" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P9" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="10" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F10" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G10" s="4" t="e">
@@ -1821,11 +1850,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H10" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I10" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J10" s="4" t="e">
@@ -1833,15 +1862,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K10" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L10" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M10" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N10" s="4" t="e">
@@ -1849,18 +1878,18 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O10" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P10" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q10" s="15"/>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Q10" s="13"/>
     </row>
     <row r="11" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F11" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G11" s="4" t="e">
@@ -1868,11 +1897,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H11" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I11" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J11" s="4" t="e">
@@ -1880,15 +1909,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K11" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L11" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M11" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N11" s="4" t="e">
@@ -1896,17 +1925,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O11" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P11" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="12" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F12" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G12" s="4" t="e">
@@ -1914,11 +1943,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H12" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I12" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J12" s="4" t="e">
@@ -1926,15 +1955,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K12" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L12" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M12" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N12" s="4" t="e">
@@ -1942,17 +1971,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O12" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P12" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="13" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F13" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G13" s="4" t="e">
@@ -1960,11 +1989,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H13" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I13" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J13" s="4" t="e">
@@ -1972,15 +2001,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K13" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L13" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M13" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N13" s="4" t="e">
@@ -1988,17 +2017,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O13" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P13" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="14" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F14" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G14" s="4" t="e">
@@ -2006,11 +2035,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H14" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I14" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J14" s="4" t="e">
@@ -2018,15 +2047,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K14" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L14" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M14" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N14" s="4" t="e">
@@ -2034,17 +2063,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O14" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P14" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="15" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F15" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G15" s="4" t="e">
@@ -2052,11 +2081,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H15" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I15" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J15" s="4" t="e">
@@ -2064,15 +2093,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K15" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L15" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M15" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N15" s="4" t="e">
@@ -2080,17 +2109,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O15" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P15" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="16" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F16" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G16" s="4" t="e">
@@ -2098,11 +2127,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H16" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I16" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J16" s="4" t="e">
@@ -2110,15 +2139,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K16" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L16" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M16" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N16" s="4" t="e">
@@ -2126,17 +2155,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O16" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P16" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="17" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F17" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G17" s="4" t="e">
@@ -2144,11 +2173,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H17" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I17" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J17" s="4" t="e">
@@ -2156,15 +2185,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K17" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L17" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M17" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N17" s="4" t="e">
@@ -2172,17 +2201,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O17" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P17" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="18" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F18" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G18" s="4" t="e">
@@ -2190,11 +2219,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H18" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I18" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J18" s="4" t="e">
@@ -2202,15 +2231,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K18" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L18" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M18" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N18" s="4" t="e">
@@ -2218,17 +2247,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O18" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P18" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="19" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F19" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G19" s="4" t="e">
@@ -2236,11 +2265,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H19" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I19" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J19" s="4" t="e">
@@ -2248,15 +2277,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K19" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L19" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M19" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N19" s="4" t="e">
@@ -2264,17 +2293,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O19" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P19" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="20" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F20" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G20" s="4" t="e">
@@ -2282,11 +2311,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H20" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I20" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J20" s="4" t="e">
@@ -2294,15 +2323,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K20" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L20" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M20" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N20" s="4" t="e">
@@ -2310,17 +2339,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O20" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P20" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="21" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F21" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G21" s="4" t="e">
@@ -2328,11 +2357,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H21" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I21" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J21" s="4" t="e">
@@ -2340,15 +2369,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K21" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L21" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M21" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N21" s="4" t="e">
@@ -2356,17 +2385,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O21" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P21" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="22" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F22" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G22" s="4" t="e">
@@ -2374,11 +2403,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H22" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I22" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J22" s="4" t="e">
@@ -2386,15 +2415,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K22" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L22" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M22" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N22" s="4" t="e">
@@ -2402,17 +2431,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O22" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P22" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="23" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F23" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G23" s="4" t="e">
@@ -2420,11 +2449,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H23" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I23" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J23" s="4" t="e">
@@ -2432,15 +2461,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K23" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L23" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M23" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N23" s="4" t="e">
@@ -2448,17 +2477,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O23" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P23" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="24" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F24" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G24" s="4" t="e">
@@ -2466,11 +2495,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H24" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I24" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J24" s="4" t="e">
@@ -2478,15 +2507,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K24" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L24" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M24" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N24" s="4" t="e">
@@ -2494,17 +2523,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O24" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P24" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="25" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F25" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G25" s="4" t="e">
@@ -2512,11 +2541,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H25" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I25" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J25" s="4" t="e">
@@ -2524,15 +2553,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K25" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L25" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M25" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N25" s="4" t="e">
@@ -2540,17 +2569,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O25" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P25" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="26" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F26" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G26" s="4" t="e">
@@ -2558,11 +2587,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H26" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I26" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J26" s="4" t="e">
@@ -2570,15 +2599,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K26" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L26" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M26" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N26" s="4" t="e">
@@ -2586,17 +2615,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O26" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P26" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="27" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F27" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G27" s="4" t="e">
@@ -2604,11 +2633,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H27" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I27" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J27" s="4" t="e">
@@ -2616,15 +2645,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K27" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L27" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M27" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N27" s="4" t="e">
@@ -2632,17 +2661,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O27" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P27" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="28" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F28" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G28" s="4" t="e">
@@ -2650,11 +2679,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H28" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I28" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J28" s="4" t="e">
@@ -2662,15 +2691,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K28" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L28" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M28" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N28" s="4" t="e">
@@ -2678,17 +2707,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O28" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P28" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="29" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F29" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G29" s="4" t="e">
@@ -2696,11 +2725,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H29" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I29" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J29" s="4" t="e">
@@ -2708,15 +2737,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K29" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L29" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M29" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N29" s="4" t="e">
@@ -2724,17 +2753,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O29" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P29" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="30" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F30" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G30" s="4" t="e">
@@ -2742,11 +2771,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H30" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I30" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J30" s="4" t="e">
@@ -2754,15 +2783,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K30" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L30" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M30" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N30" s="4" t="e">
@@ -2770,17 +2799,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O30" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P30" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="31" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F31" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G31" s="4" t="e">
@@ -2788,11 +2817,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H31" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I31" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J31" s="4" t="e">
@@ -2800,15 +2829,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K31" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L31" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M31" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N31" s="4" t="e">
@@ -2816,17 +2845,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O31" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P31" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="32" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F32" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G32" s="4" t="e">
@@ -2834,11 +2863,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H32" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I32" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J32" s="4" t="e">
@@ -2846,15 +2875,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K32" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L32" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M32" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N32" s="4" t="e">
@@ -2862,17 +2891,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O32" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P32" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="33" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F33" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G33" s="4" t="e">
@@ -2880,11 +2909,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H33" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I33" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J33" s="4" t="e">
@@ -2892,15 +2921,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K33" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L33" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M33" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N33" s="4" t="e">
@@ -2908,17 +2937,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O33" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P33" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="34" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F34" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G34" s="4" t="e">
@@ -2926,11 +2955,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H34" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I34" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J34" s="4" t="e">
@@ -2938,15 +2967,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K34" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L34" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M34" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N34" s="4" t="e">
@@ -2954,17 +2983,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O34" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P34" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="35" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F35" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G35" s="4" t="e">
@@ -2972,11 +3001,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H35" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I35" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J35" s="4" t="e">
@@ -2984,15 +3013,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K35" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L35" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M35" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N35" s="4" t="e">
@@ -3000,17 +3029,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O35" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P35" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="36" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F36" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G36" s="4" t="e">
@@ -3018,11 +3047,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H36" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I36" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J36" s="4" t="e">
@@ -3030,15 +3059,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K36" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L36" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M36" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N36" s="4" t="e">
@@ -3046,17 +3075,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O36" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P36" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="37" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F37" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G37" s="4" t="e">
@@ -3064,11 +3093,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H37" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I37" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J37" s="4" t="e">
@@ -3076,15 +3105,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K37" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L37" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M37" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N37" s="4" t="e">
@@ -3092,17 +3121,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O37" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P37" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="38" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F38" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G38" s="4" t="e">
@@ -3110,11 +3139,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H38" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I38" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J38" s="4" t="e">
@@ -3122,15 +3151,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K38" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L38" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M38" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N38" s="4" t="e">
@@ -3138,17 +3167,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O38" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P38" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="39" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F39" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G39" s="4" t="e">
@@ -3156,11 +3185,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H39" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I39" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J39" s="4" t="e">
@@ -3168,15 +3197,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K39" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L39" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M39" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N39" s="4" t="e">
@@ -3184,17 +3213,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O39" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P39" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="40" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F40" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G40" s="4" t="e">
@@ -3202,11 +3231,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H40" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I40" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J40" s="4" t="e">
@@ -3214,15 +3243,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K40" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L40" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M40" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N40" s="4" t="e">
@@ -3230,17 +3259,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O40" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P40" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="41" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F41" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G41" s="4" t="e">
@@ -3248,11 +3277,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H41" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I41" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J41" s="4" t="e">
@@ -3260,15 +3289,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K41" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L41" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M41" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N41" s="4" t="e">
@@ -3276,17 +3305,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O41" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P41" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="42" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F42" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G42" s="4" t="e">
@@ -3294,11 +3323,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H42" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I42" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J42" s="4" t="e">
@@ -3306,15 +3335,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K42" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L42" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M42" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N42" s="4" t="e">
@@ -3322,17 +3351,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O42" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P42" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="43" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F43" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G43" s="4" t="e">
@@ -3340,11 +3369,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H43" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I43" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J43" s="4" t="e">
@@ -3352,15 +3381,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K43" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L43" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M43" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N43" s="4" t="e">
@@ -3368,17 +3397,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O43" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P43" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="44" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F44" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G44" s="4" t="e">
@@ -3386,11 +3415,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H44" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I44" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J44" s="4" t="e">
@@ -3398,15 +3427,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K44" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L44" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M44" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N44" s="4" t="e">
@@ -3414,17 +3443,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O44" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P44" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="45" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F45" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G45" s="4" t="e">
@@ -3432,11 +3461,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H45" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I45" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J45" s="4" t="e">
@@ -3444,15 +3473,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K45" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L45" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M45" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N45" s="4" t="e">
@@ -3460,17 +3489,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O45" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P45" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="46" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F46" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G46" s="4" t="e">
@@ -3478,11 +3507,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H46" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I46" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J46" s="4" t="e">
@@ -3490,15 +3519,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K46" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L46" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M46" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N46" s="4" t="e">
@@ -3506,17 +3535,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O46" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P46" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="47" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F47" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G47" s="4" t="e">
@@ -3524,11 +3553,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H47" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I47" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J47" s="4" t="e">
@@ -3536,15 +3565,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K47" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L47" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M47" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N47" s="4" t="e">
@@ -3552,17 +3581,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O47" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P47" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="48" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F48" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G48" s="4" t="e">
@@ -3570,11 +3599,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H48" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I48" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J48" s="4" t="e">
@@ -3582,15 +3611,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K48" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L48" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M48" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N48" s="4" t="e">
@@ -3598,17 +3627,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O48" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P48" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="49" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F49" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G49" s="4" t="e">
@@ -3616,11 +3645,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H49" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I49" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J49" s="4" t="e">
@@ -3628,15 +3657,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K49" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L49" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M49" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N49" s="4" t="e">
@@ -3644,17 +3673,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O49" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P49" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="50" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F50" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G50" s="4" t="e">
@@ -3662,11 +3691,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H50" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I50" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J50" s="4" t="e">
@@ -3674,15 +3703,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K50" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L50" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M50" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N50" s="4" t="e">
@@ -3690,17 +3719,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O50" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P50" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="51" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F51" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G51" s="4" t="e">
@@ -3708,11 +3737,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H51" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I51" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J51" s="4" t="e">
@@ -3720,15 +3749,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K51" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L51" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M51" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N51" s="4" t="e">
@@ -3736,17 +3765,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O51" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P51" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="52" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F52" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G52" s="4" t="e">
@@ -3754,11 +3783,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H52" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I52" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J52" s="4" t="e">
@@ -3766,15 +3795,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K52" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L52" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M52" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N52" s="4" t="e">
@@ -3782,17 +3811,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O52" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P52" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="53" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F53" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G53" s="4" t="e">
@@ -3800,11 +3829,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H53" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I53" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J53" s="4" t="e">
@@ -3812,15 +3841,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K53" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L53" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M53" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N53" s="4" t="e">
@@ -3828,17 +3857,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O53" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P53" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="54" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F54" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G54" s="4" t="e">
@@ -3846,11 +3875,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H54" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I54" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J54" s="4" t="e">
@@ -3858,15 +3887,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K54" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L54" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M54" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N54" s="4" t="e">
@@ -3874,17 +3903,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O54" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P54" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="55" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F55" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G55" s="4" t="e">
@@ -3892,11 +3921,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H55" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I55" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J55" s="4" t="e">
@@ -3904,15 +3933,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K55" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L55" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M55" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N55" s="4" t="e">
@@ -3920,17 +3949,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O55" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P55" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="56" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F56" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G56" s="4" t="e">
@@ -3938,11 +3967,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H56" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I56" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J56" s="4" t="e">
@@ -3950,15 +3979,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K56" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L56" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M56" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N56" s="4" t="e">
@@ -3966,17 +3995,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O56" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P56" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="57" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F57" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G57" s="4" t="e">
@@ -3984,11 +4013,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H57" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I57" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J57" s="4" t="e">
@@ -3996,15 +4025,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K57" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L57" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M57" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N57" s="4" t="e">
@@ -4012,17 +4041,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O57" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P57" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="58" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F58" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G58" s="4" t="e">
@@ -4030,11 +4059,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H58" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I58" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J58" s="4" t="e">
@@ -4042,15 +4071,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K58" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L58" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M58" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N58" s="4" t="e">
@@ -4058,17 +4087,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O58" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P58" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="59" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F59" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G59" s="4" t="e">
@@ -4076,11 +4105,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H59" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I59" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J59" s="4" t="e">
@@ -4088,15 +4117,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K59" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L59" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M59" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N59" s="4" t="e">
@@ -4104,17 +4133,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O59" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P59" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="60" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F60" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G60" s="4" t="e">
@@ -4122,11 +4151,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H60" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I60" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J60" s="4" t="e">
@@ -4134,15 +4163,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K60" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L60" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M60" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N60" s="4" t="e">
@@ -4150,17 +4179,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O60" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P60" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="61" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F61" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G61" s="4" t="e">
@@ -4168,11 +4197,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H61" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I61" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J61" s="4" t="e">
@@ -4180,15 +4209,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K61" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L61" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M61" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N61" s="4" t="e">
@@ -4196,17 +4225,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O61" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P61" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="62" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F62" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G62" s="4" t="e">
@@ -4214,11 +4243,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H62" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I62" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J62" s="4" t="e">
@@ -4226,15 +4255,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K62" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L62" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M62" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N62" s="4" t="e">
@@ -4242,17 +4271,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O62" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P62" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="63" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F63" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G63" s="4" t="e">
@@ -4260,11 +4289,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H63" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I63" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J63" s="4" t="e">
@@ -4272,15 +4301,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K63" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L63" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M63" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N63" s="4" t="e">
@@ -4288,17 +4317,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O63" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P63" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="64" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F64" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G64" s="4" t="e">
@@ -4306,11 +4335,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H64" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I64" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J64" s="4" t="e">
@@ -4318,15 +4347,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K64" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L64" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M64" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N64" s="4" t="e">
@@ -4334,17 +4363,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O64" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P64" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="65" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F65" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G65" s="4" t="e">
@@ -4352,11 +4381,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H65" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I65" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J65" s="4" t="e">
@@ -4364,15 +4393,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K65" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L65" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M65" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N65" s="4" t="e">
@@ -4380,17 +4409,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O65" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P65" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="66" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F66" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G66" s="4" t="e">
@@ -4398,11 +4427,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H66" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I66" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J66" s="4" t="e">
@@ -4410,15 +4439,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K66" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L66" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M66" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N66" s="4" t="e">
@@ -4426,17 +4455,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O66" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P66" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="67" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F67" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G67" s="4" t="e">
@@ -4444,11 +4473,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H67" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I67" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J67" s="4" t="e">
@@ -4456,15 +4485,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K67" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L67" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M67" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N67" s="4" t="e">
@@ -4472,17 +4501,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O67" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P67" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="68" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F68" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G68" s="4" t="e">
@@ -4490,11 +4519,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H68" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I68" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J68" s="4" t="e">
@@ -4502,15 +4531,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K68" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L68" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M68" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N68" s="4" t="e">
@@ -4518,17 +4547,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O68" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P68" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="69" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F69" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G69" s="4" t="e">
@@ -4536,11 +4565,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H69" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I69" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J69" s="4" t="e">
@@ -4548,15 +4577,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K69" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L69" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M69" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N69" s="4" t="e">
@@ -4564,17 +4593,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O69" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P69" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="70" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F70" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G70" s="4" t="e">
@@ -4582,11 +4611,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H70" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I70" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J70" s="4" t="e">
@@ -4594,15 +4623,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K70" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L70" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M70" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N70" s="4" t="e">
@@ -4610,17 +4639,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O70" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P70" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="71" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F71" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G71" s="4" t="e">
@@ -4628,11 +4657,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H71" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I71" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J71" s="4" t="e">
@@ -4640,15 +4669,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K71" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L71" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M71" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N71" s="4" t="e">
@@ -4656,17 +4685,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O71" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P71" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="72" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F72" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G72" s="4" t="e">
@@ -4674,11 +4703,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H72" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I72" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J72" s="4" t="e">
@@ -4686,15 +4715,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K72" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L72" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M72" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N72" s="4" t="e">
@@ -4702,17 +4731,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O72" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P72" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="73" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F73" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G73" s="4" t="e">
@@ -4720,11 +4749,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H73" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I73" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J73" s="4" t="e">
@@ -4732,15 +4761,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K73" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L73" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M73" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N73" s="4" t="e">
@@ -4748,17 +4777,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O73" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P73" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="74" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F74" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G74" s="4" t="e">
@@ -4766,11 +4795,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H74" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I74" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J74" s="4" t="e">
@@ -4778,15 +4807,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K74" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L74" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M74" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N74" s="4" t="e">
@@ -4794,17 +4823,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O74" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P74" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="75" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F75" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G75" s="4" t="e">
@@ -4812,11 +4841,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H75" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I75" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J75" s="4" t="e">
@@ -4824,15 +4853,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K75" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L75" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M75" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N75" s="4" t="e">
@@ -4840,17 +4869,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O75" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P75" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="76" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F76" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G76" s="4" t="e">
@@ -4858,11 +4887,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H76" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I76" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J76" s="4" t="e">
@@ -4870,15 +4899,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K76" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L76" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M76" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N76" s="4" t="e">
@@ -4886,17 +4915,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O76" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P76" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="77" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F77" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G77" s="4" t="e">
@@ -4904,11 +4933,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H77" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I77" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J77" s="4" t="e">
@@ -4916,15 +4945,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K77" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L77" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M77" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N77" s="4" t="e">
@@ -4932,17 +4961,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O77" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P77" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="78" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F78" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G78" s="4" t="e">
@@ -4950,11 +4979,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H78" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I78" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J78" s="4" t="e">
@@ -4962,15 +4991,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K78" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L78" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M78" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N78" s="4" t="e">
@@ -4978,17 +5007,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O78" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P78" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="79" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F79" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G79" s="4" t="e">
@@ -4996,11 +5025,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H79" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I79" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J79" s="4" t="e">
@@ -5008,15 +5037,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K79" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L79" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M79" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N79" s="4" t="e">
@@ -5024,17 +5053,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O79" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P79" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="80" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F80" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G80" s="4" t="e">
@@ -5042,11 +5071,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H80" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I80" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J80" s="4" t="e">
@@ -5054,15 +5083,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K80" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L80" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M80" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N80" s="4" t="e">
@@ -5070,17 +5099,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O80" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P80" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="81" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F81" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G81" s="4" t="e">
@@ -5088,11 +5117,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H81" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I81" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J81" s="4" t="e">
@@ -5100,15 +5129,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K81" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L81" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M81" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N81" s="4" t="e">
@@ -5116,17 +5145,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O81" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P81" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="82" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F82" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G82" s="4" t="e">
@@ -5134,11 +5163,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H82" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I82" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J82" s="4" t="e">
@@ -5146,15 +5175,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K82" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L82" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M82" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N82" s="4" t="e">
@@ -5162,17 +5191,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O82" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P82" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="83" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F83" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G83" s="4" t="e">
@@ -5180,11 +5209,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H83" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I83" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J83" s="4" t="e">
@@ -5192,15 +5221,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K83" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L83" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M83" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N83" s="4" t="e">
@@ -5208,17 +5237,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O83" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P83" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="84" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F84" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G84" s="4" t="e">
@@ -5226,11 +5255,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H84" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I84" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J84" s="4" t="e">
@@ -5238,15 +5267,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K84" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L84" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M84" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N84" s="4" t="e">
@@ -5254,17 +5283,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O84" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P84" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="85" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F85" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G85" s="4" t="e">
@@ -5272,11 +5301,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H85" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I85" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J85" s="4" t="e">
@@ -5284,15 +5313,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K85" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L85" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M85" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N85" s="4" t="e">
@@ -5300,17 +5329,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O85" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P85" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="86" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F86" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G86" s="4" t="e">
@@ -5318,11 +5347,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H86" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I86" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J86" s="4" t="e">
@@ -5330,15 +5359,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K86" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L86" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M86" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N86" s="4" t="e">
@@ -5346,17 +5375,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O86" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P86" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="87" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F87" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G87" s="4" t="e">
@@ -5364,11 +5393,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H87" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I87" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J87" s="4" t="e">
@@ -5376,15 +5405,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K87" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L87" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M87" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N87" s="4" t="e">
@@ -5392,17 +5421,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O87" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P87" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="88" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F88" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G88" s="4" t="e">
@@ -5410,11 +5439,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H88" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I88" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J88" s="4" t="e">
@@ -5422,15 +5451,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K88" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L88" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M88" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N88" s="4" t="e">
@@ -5438,17 +5467,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O88" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P88" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="89" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F89" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G89" s="4" t="e">
@@ -5456,11 +5485,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H89" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I89" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J89" s="4" t="e">
@@ -5468,15 +5497,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K89" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L89" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M89" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N89" s="4" t="e">
@@ -5484,17 +5513,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O89" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P89" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="90" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F90" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G90" s="4" t="e">
@@ -5502,11 +5531,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H90" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I90" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J90" s="4" t="e">
@@ -5514,15 +5543,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K90" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L90" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M90" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N90" s="4" t="e">
@@ -5530,17 +5559,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O90" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P90" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="91" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F91" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G91" s="4" t="e">
@@ -5548,11 +5577,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H91" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I91" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J91" s="4" t="e">
@@ -5560,15 +5589,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K91" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L91" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M91" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N91" s="4" t="e">
@@ -5576,17 +5605,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O91" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P91" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="92" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F92" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G92" s="4" t="e">
@@ -5594,11 +5623,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H92" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I92" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J92" s="4" t="e">
@@ -5606,15 +5635,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K92" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L92" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M92" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N92" s="4" t="e">
@@ -5622,17 +5651,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O92" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P92" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="93" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F93" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G93" s="4" t="e">
@@ -5640,11 +5669,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H93" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I93" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J93" s="4" t="e">
@@ -5652,15 +5681,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K93" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L93" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M93" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N93" s="4" t="e">
@@ -5668,17 +5697,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O93" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P93" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="94" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F94" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G94" s="4" t="e">
@@ -5686,11 +5715,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H94" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I94" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J94" s="4" t="e">
@@ -5698,15 +5727,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K94" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L94" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M94" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N94" s="4" t="e">
@@ -5714,17 +5743,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O94" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P94" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="95" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F95" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G95" s="4" t="e">
@@ -5732,11 +5761,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H95" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I95" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J95" s="4" t="e">
@@ -5744,15 +5773,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K95" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L95" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M95" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N95" s="4" t="e">
@@ -5760,17 +5789,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O95" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P95" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="96" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F96" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G96" s="4" t="e">
@@ -5778,11 +5807,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H96" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I96" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J96" s="4" t="e">
@@ -5790,15 +5819,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K96" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L96" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M96" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N96" s="4" t="e">
@@ -5806,17 +5835,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O96" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P96" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="97" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F97" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G97" s="4" t="e">
@@ -5824,11 +5853,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H97" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I97" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J97" s="4" t="e">
@@ -5836,15 +5865,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K97" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L97" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M97" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N97" s="4" t="e">
@@ -5852,17 +5881,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O97" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P97" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="98" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F98" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G98" s="4" t="e">
@@ -5870,11 +5899,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H98" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I98" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J98" s="4" t="e">
@@ -5882,15 +5911,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K98" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L98" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M98" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N98" s="4" t="e">
@@ -5898,17 +5927,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O98" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P98" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="99" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F99" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G99" s="4" t="e">
@@ -5916,11 +5945,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H99" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I99" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J99" s="4" t="e">
@@ -5928,15 +5957,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K99" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L99" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M99" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N99" s="4" t="e">
@@ -5944,17 +5973,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O99" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P99" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="100" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F100" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G100" s="4" t="e">
@@ -5962,11 +5991,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H100" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I100" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J100" s="4" t="e">
@@ -5974,15 +6003,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K100" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L100" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M100" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N100" s="4" t="e">
@@ -5990,17 +6019,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O100" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P100" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="101" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F101" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G101" s="4" t="e">
@@ -6008,11 +6037,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H101" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I101" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J101" s="4" t="e">
@@ -6020,15 +6049,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K101" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L101" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M101" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N101" s="4" t="e">
@@ -6036,17 +6065,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O101" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P101" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="102" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F102" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G102" s="4" t="e">
@@ -6054,11 +6083,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H102" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I102" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J102" s="4" t="e">
@@ -6066,15 +6095,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K102" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L102" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M102" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N102" s="4" t="e">
@@ -6082,17 +6111,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O102" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P102" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="103" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F103" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G103" s="4" t="e">
@@ -6100,11 +6129,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H103" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I103" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J103" s="4" t="e">
@@ -6112,15 +6141,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K103" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L103" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M103" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N103" s="4" t="e">
@@ -6128,17 +6157,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O103" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P103" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="104" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F104" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G104" s="4" t="e">
@@ -6146,11 +6175,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H104" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I104" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J104" s="4" t="e">
@@ -6158,15 +6187,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K104" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L104" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M104" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N104" s="4" t="e">
@@ -6174,17 +6203,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O104" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P104" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="105" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F105" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G105" s="4" t="e">
@@ -6192,11 +6221,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H105" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I105" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J105" s="4" t="e">
@@ -6204,15 +6233,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K105" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L105" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M105" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N105" s="4" t="e">
@@ -6220,17 +6249,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O105" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P105" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="106" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F106" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G106" s="4" t="e">
@@ -6238,11 +6267,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H106" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I106" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J106" s="4" t="e">
@@ -6250,15 +6279,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K106" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L106" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M106" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N106" s="4" t="e">
@@ -6266,17 +6295,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O106" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P106" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="107" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F107" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G107" s="4" t="e">
@@ -6284,11 +6313,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H107" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I107" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J107" s="4" t="e">
@@ -6296,15 +6325,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K107" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L107" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M107" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N107" s="4" t="e">
@@ -6312,17 +6341,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O107" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P107" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="108" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F108" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G108" s="4" t="e">
@@ -6330,11 +6359,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H108" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I108" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J108" s="4" t="e">
@@ -6342,15 +6371,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K108" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L108" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M108" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N108" s="4" t="e">
@@ -6358,17 +6387,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O108" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P108" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="109" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F109" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G109" s="4" t="e">
@@ -6376,11 +6405,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H109" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I109" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J109" s="4" t="e">
@@ -6388,15 +6417,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K109" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L109" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M109" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N109" s="4" t="e">
@@ -6404,17 +6433,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O109" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P109" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="110" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F110" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G110" s="4" t="e">
@@ -6422,11 +6451,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H110" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I110" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J110" s="4" t="e">
@@ -6434,15 +6463,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K110" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L110" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M110" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N110" s="4" t="e">
@@ -6450,17 +6479,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O110" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P110" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="111" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F111" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G111" s="4" t="e">
@@ -6468,11 +6497,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H111" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I111" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J111" s="4" t="e">
@@ -6480,15 +6509,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K111" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L111" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M111" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N111" s="4" t="e">
@@ -6496,17 +6525,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O111" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P111" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="112" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F112" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G112" s="4" t="e">
@@ -6514,11 +6543,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H112" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I112" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J112" s="4" t="e">
@@ -6526,15 +6555,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K112" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L112" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M112" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N112" s="4" t="e">
@@ -6542,17 +6571,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O112" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P112" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="113" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F113" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G113" s="4" t="e">
@@ -6560,11 +6589,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H113" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I113" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J113" s="4" t="e">
@@ -6572,15 +6601,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K113" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L113" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M113" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N113" s="4" t="e">
@@ -6588,17 +6617,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O113" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P113" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="114" spans="6:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F114" s="3" t="e">
-        <f>(12-Table6[[#This Row],[Prąd 24V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 24V]]*PI()/30)*1000</f>
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G114" s="4" t="e">
@@ -6606,11 +6635,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="H114" s="5" t="e">
-        <f>Table6[[#This Row],[Stała momentu '[Nm/mA']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 24V '[mA']]]/1000)</f>
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I114" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 24V]]</f>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J114" s="4" t="e">
@@ -6618,15 +6647,15 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K114" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L114" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M114" s="3">
-        <f>Table6[[#This Row],[RPM 24V]]*$S$3/24</f>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
         <v>0</v>
       </c>
       <c r="N114" s="4" t="e">
@@ -6634,11 +6663,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O114" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P114" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[Nm/A']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -6646,7 +6675,7 @@
   <mergeCells count="1">
     <mergeCell ref="R1:S1"/>
   </mergeCells>
-  <conditionalFormatting sqref="A1:P6">
+  <conditionalFormatting sqref="A1:P2 A3:E6 I3:P6 F3:G114 H3:H115">
     <cfRule type="expression" dxfId="1" priority="1">
       <formula>$K1=_xlfn.AGGREGATE(4,6,$K:$K)</formula>
     </cfRule>

--- a/SilniczkiExcel.xlsx
+++ b/SilniczkiExcel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\tech\robotyka\robots\evangelion-turbo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B222485A-06DA-40D6-93BA-7D8521B89717}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E2355DB-D683-4D55-A9AD-EBBE2B44594A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="480" windowWidth="29040" windowHeight="15840" xr2:uid="{511008C5-3BC9-4B59-854A-53C66BDAD283}"/>
+    <workbookView xWindow="-28920" yWindow="3300" windowWidth="29040" windowHeight="15840" xr2:uid="{511008C5-3BC9-4B59-854A-53C66BDAD283}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>Nazwa</t>
   </si>
@@ -45,9 +45,6 @@
   </si>
   <si>
     <t>Waga</t>
-  </si>
-  <si>
-    <t>RK-385P-2175</t>
   </si>
   <si>
     <t>JOHNSON HC383MG RS380</t>
@@ -107,9 +104,6 @@
     <t>RS-360ST-2885</t>
   </si>
   <si>
-    <t>pololu 37d HP 12v</t>
-  </si>
-  <si>
     <t>Moment [Nm] (Dane U)</t>
   </si>
   <si>
@@ -123,6 +117,9 @@
   </si>
   <si>
     <t>Moment w zwarciu 12V [mNm]</t>
+  </si>
+  <si>
+    <t>RK-385PR-2175</t>
   </si>
 </sst>
 </file>
@@ -442,29 +439,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="24">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.749961851863155"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.749961851863155"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="22">
     <dxf>
       <font>
         <b val="0"/>
@@ -502,12 +477,8 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -516,7 +487,9 @@
         <left style="thin">
           <color indexed="64"/>
         </left>
-        <right/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
         <top style="thin">
           <color indexed="64"/>
         </top>
@@ -542,12 +515,8 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -557,6 +526,25 @@
           <color indexed="64"/>
         </left>
         <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
           <color indexed="64"/>
         </right>
         <top style="thin">
@@ -579,44 +567,15 @@
         <left style="thin">
           <color indexed="64"/>
         </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
+        <right/>
         <top style="thin">
           <color indexed="64"/>
         </top>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -896,46 +855,46 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{AC265550-FF17-485F-9292-5B99975F35F1}" name="Table6" displayName="Table6" ref="A1:P1048576" totalsRowShown="0" headerRowDxfId="23" headerRowBorderDxfId="22" tableBorderDxfId="21" totalsRowBorderDxfId="20">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{AC265550-FF17-485F-9292-5B99975F35F1}" name="Table6" displayName="Table6" ref="A1:P1048576" totalsRowShown="0" headerRowDxfId="21" headerRowBorderDxfId="20" tableBorderDxfId="19" totalsRowBorderDxfId="18">
   <autoFilter ref="A1:P1048576" xr:uid="{AC265550-FF17-485F-9292-5B99975F35F1}"/>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{F9A7EC63-1D4A-4C94-8631-E9F11B91398D}" name="Nazwa" dataDxfId="19"/>
-    <tableColumn id="2" xr3:uid="{276B8804-5769-4B88-907D-9FC75BD252C8}" name="Waga" dataDxfId="18"/>
-    <tableColumn id="4" xr3:uid="{F4A061AF-E573-4F92-8E59-AEC883A58204}" name="Opór uzwojeń [U/1A]" dataDxfId="17"/>
-    <tableColumn id="5" xr3:uid="{A44E980B-70F8-4B74-AF97-3C900A21C351}" name="RPM 12V" dataDxfId="16"/>
-    <tableColumn id="6" xr3:uid="{776A220E-593B-4B22-AB1F-214C9A436F19}" name="Prąd 12V [mA]" dataDxfId="15"/>
-    <tableColumn id="7" xr3:uid="{199A7165-012B-4850-A0FE-5761864209B2}" name="Stała momentu [mNm/A]" dataDxfId="14">
+    <tableColumn id="1" xr3:uid="{F9A7EC63-1D4A-4C94-8631-E9F11B91398D}" name="Nazwa" dataDxfId="17"/>
+    <tableColumn id="2" xr3:uid="{276B8804-5769-4B88-907D-9FC75BD252C8}" name="Waga" dataDxfId="16"/>
+    <tableColumn id="4" xr3:uid="{F4A061AF-E573-4F92-8E59-AEC883A58204}" name="Opór uzwojeń [U/1A]" dataDxfId="15"/>
+    <tableColumn id="5" xr3:uid="{A44E980B-70F8-4B74-AF97-3C900A21C351}" name="RPM 12V" dataDxfId="14"/>
+    <tableColumn id="6" xr3:uid="{776A220E-593B-4B22-AB1F-214C9A436F19}" name="Prąd 12V [mA]" dataDxfId="13"/>
+    <tableColumn id="7" xr3:uid="{199A7165-012B-4850-A0FE-5761864209B2}" name="Stała momentu [mNm/A]" dataDxfId="12">
       <calculatedColumnFormula>(12-Table6[[#This Row],[Prąd 12V '[mA']]]/10000*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{55F3429F-8468-494B-B971-71BCE955500A}" name="Prąd w zwarciu 12V [A]" dataDxfId="13">
+    <tableColumn id="17" xr3:uid="{55F3429F-8468-494B-B971-71BCE955500A}" name="Prąd w zwarciu 12V [A]" dataDxfId="11">
       <calculatedColumnFormula>12/Table6[[#This Row],[Opór uzwojeń '[U/1A']]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{7EFBC617-C9B9-4B2D-8DC9-69B3B4A9327E}" name="Moment w zwarciu 12V [mNm]" dataDxfId="12">
+    <tableColumn id="18" xr3:uid="{7EFBC617-C9B9-4B2D-8DC9-69B3B4A9327E}" name="Moment w zwarciu 12V [mNm]" dataDxfId="10">
       <calculatedColumnFormula>Table6[[#This Row],[Stała momentu '[mNm/A']]]*(Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]-Table6[[#This Row],[Prąd 12V '[mA']]]/1000)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{69CD1EDF-51AC-407C-9E31-80182F0F74C6}" name="Napięcie (Dane RPM)" dataDxfId="11">
+    <tableColumn id="13" xr3:uid="{458715B8-2553-4AFB-BD1A-63EFEC89C3AF}" name="RPM (Dane U)" dataDxfId="9">
+      <calculatedColumnFormula>Table6[[#This Row],[RPM 12V]]*$S$3/24</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="15" xr3:uid="{E50BDF0E-1B89-4839-B5C1-10C416C379A0}" name="Prąd w zwarciu (Dane U)" dataDxfId="8">
+      <calculatedColumnFormula>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="19" xr3:uid="{8C6AAA0F-FBFF-4B85-A456-65D77F8FF3CF}" name="Moment [Nm] (Dane U)" dataDxfId="7">
+      <calculatedColumnFormula>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="16" xr3:uid="{DD076DF6-AE6B-40EE-84ED-FD4D6650BC91}" name="[Nm/g] (Dane U)" dataDxfId="6">
+      <calculatedColumnFormula>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="8" xr3:uid="{69CD1EDF-51AC-407C-9E31-80182F0F74C6}" name="Napięcie (Dane RPM)" dataDxfId="5">
       <calculatedColumnFormula>$S$2*24/Table6[[#This Row],[RPM 12V]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{68200736-7943-41FD-A9E9-CE88B52BBDBE}" name="Prąd w zwarciu (Dane RPM)" dataDxfId="10">
+    <tableColumn id="10" xr3:uid="{68200736-7943-41FD-A9E9-CE88B52BBDBE}" name="Prąd w zwarciu (Dane RPM)" dataDxfId="4">
       <calculatedColumnFormula>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{4295B029-6DEF-402F-8CEA-5C0420380648}" name="Moment (Dane RPM)" dataDxfId="9">
+    <tableColumn id="11" xr3:uid="{4295B029-6DEF-402F-8CEA-5C0420380648}" name="Moment (Dane RPM)" dataDxfId="3">
       <calculatedColumnFormula>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{9518D69E-613C-4364-BA73-1234317D9EAB}" name="[Nm/g] (Dane RPM)" dataDxfId="8">
+    <tableColumn id="12" xr3:uid="{9518D69E-613C-4364-BA73-1234317D9EAB}" name="[Nm/g] (Dane RPM)" dataDxfId="2">
       <calculatedColumnFormula>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="13" xr3:uid="{458715B8-2553-4AFB-BD1A-63EFEC89C3AF}" name="RPM (Dane U)" dataDxfId="7">
-      <calculatedColumnFormula>Table6[[#This Row],[RPM 12V]]*$S$3/24</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="15" xr3:uid="{E50BDF0E-1B89-4839-B5C1-10C416C379A0}" name="Prąd w zwarciu (Dane U)" dataDxfId="6">
-      <calculatedColumnFormula>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="19" xr3:uid="{8C6AAA0F-FBFF-4B85-A456-65D77F8FF3CF}" name="Moment [Nm] (Dane U)" dataDxfId="5">
-      <calculatedColumnFormula>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="16" xr3:uid="{DD076DF6-AE6B-40EE-84ED-FD4D6650BC91}" name="[Nm/g] (Dane U)" dataDxfId="4">
-      <calculatedColumnFormula>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1270,14 +1229,14 @@
     <col min="6" max="6" width="26.140625" style="3" customWidth="1"/>
     <col min="7" max="7" width="23.42578125" style="4" customWidth="1"/>
     <col min="8" max="8" width="30.42578125" style="5" customWidth="1"/>
-    <col min="9" max="9" width="21.7109375" style="3" customWidth="1"/>
-    <col min="10" max="10" width="26.140625" style="4" customWidth="1"/>
-    <col min="11" max="11" width="21" style="4" customWidth="1"/>
-    <col min="12" max="12" width="20" style="5" customWidth="1"/>
-    <col min="13" max="13" width="16" style="3" customWidth="1"/>
-    <col min="14" max="14" width="24.140625" style="4" customWidth="1"/>
-    <col min="15" max="15" width="28.42578125" style="7" customWidth="1"/>
-    <col min="16" max="16" width="17.85546875" style="5" customWidth="1"/>
+    <col min="9" max="9" width="16" style="3" customWidth="1"/>
+    <col min="10" max="10" width="24.140625" style="4" customWidth="1"/>
+    <col min="11" max="11" width="28.42578125" style="7" customWidth="1"/>
+    <col min="12" max="12" width="17.85546875" style="5" customWidth="1"/>
+    <col min="13" max="13" width="21.7109375" style="3" customWidth="1"/>
+    <col min="14" max="14" width="26.140625" style="4" customWidth="1"/>
+    <col min="15" max="15" width="21" style="4" customWidth="1"/>
+    <col min="16" max="16" width="20" style="5" customWidth="1"/>
     <col min="17" max="17" width="6.28515625" customWidth="1"/>
     <col min="18" max="18" width="27.42578125" customWidth="1"/>
   </cols>
@@ -1290,49 +1249,49 @@
         <v>2</v>
       </c>
       <c r="C1" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="E1" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="H1" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="E1" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="10" t="s">
+      <c r="I1" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="H1" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="I1" s="9" t="s">
+      <c r="K1" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="O1" s="10" t="s">
         <v>9</v>
-      </c>
-      <c r="K1" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="M1" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="N1" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="O1" s="12" t="s">
-        <v>24</v>
       </c>
       <c r="P1" s="11" t="s">
         <v>17</v>
       </c>
       <c r="R1" s="19" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="S1" s="20"/>
     </row>
@@ -1344,60 +1303,60 @@
         <v>75.3</v>
       </c>
       <c r="C2" s="3">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="D2" s="4">
-        <v>10000</v>
+        <v>11900</v>
       </c>
       <c r="E2" s="7">
-        <v>123</v>
+        <v>160</v>
       </c>
       <c r="F2" s="3">
         <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
-        <v>11.224243206612826</v>
+        <v>9.3278171016816369</v>
       </c>
       <c r="G2" s="4">
         <f>12/Table6[[#This Row],[Opór uzwojeń '[U/1A']]]</f>
+        <v>5.1063829787234036</v>
+      </c>
+      <c r="H2" s="5">
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
+        <v>47.631406476672183</v>
+      </c>
+      <c r="I2" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>2975</v>
+      </c>
+      <c r="J2" s="4">
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>2.5531914893617018</v>
+      </c>
+      <c r="K2" s="7">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <v>23.815703238336095</v>
+      </c>
+      <c r="L2" s="5">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>0.31627759944669448</v>
+      </c>
+      <c r="M2" s="3">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>20.168067226890756</v>
+      </c>
+      <c r="N2" s="4">
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>8.5821562667620217</v>
+      </c>
+      <c r="O2" s="4">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>80.052783994407022</v>
+      </c>
+      <c r="P2" s="5">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <v>1.0631179813334266</v>
+      </c>
+      <c r="R2" s="14" t="s">
         <v>6</v>
-      </c>
-      <c r="H2" s="5">
-        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
-        <v>67.345459239676956</v>
-      </c>
-      <c r="I2" s="3">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>24</v>
-      </c>
-      <c r="J2" s="4">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>12</v>
-      </c>
-      <c r="K2" s="4">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>134.69091847935391</v>
-      </c>
-      <c r="L2" s="5">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>1.7887240169900918</v>
-      </c>
-      <c r="M2" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>5000</v>
-      </c>
-      <c r="N2" s="4">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>6</v>
-      </c>
-      <c r="O2" s="7">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
-        <v>67.345459239676956</v>
-      </c>
-      <c r="P2" s="5">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
-        <v>0.89436200849504588</v>
-      </c>
-      <c r="R2" s="14" t="s">
-        <v>7</v>
       </c>
       <c r="S2" s="17">
         <v>10000</v>
@@ -1405,133 +1364,134 @@
     </row>
     <row r="3" spans="1:19" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="B3" s="7">
         <v>70.7</v>
       </c>
       <c r="C3" s="3">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="D3" s="4">
-        <v>10000</v>
+        <v>9650</v>
       </c>
       <c r="E3" s="7">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="F3" s="3">
         <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
-        <v>11.091507984074187</v>
+        <v>11.366631630000345</v>
       </c>
       <c r="G3" s="4">
         <f>12/Table6[[#This Row],[Opór uzwojeń '[U/1A']]]</f>
-        <v>3.116883116883117</v>
+        <v>3.0379746835443036</v>
       </c>
       <c r="H3" s="5">
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
-        <v>34.570933976335134</v>
+        <v>34.531539129114968</v>
       </c>
       <c r="I3" s="3">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>24</v>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>2412.5</v>
       </c>
       <c r="J3" s="4">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>6.233766233766235</v>
-      </c>
-      <c r="K3" s="4">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>69.141867952670268</v>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>1.5189873417721518</v>
+      </c>
+      <c r="K3" s="7">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <v>17.265769564557484</v>
       </c>
       <c r="L3" s="5">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>0.97796135718062605</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>0.2442117335863859</v>
       </c>
       <c r="M3" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>5000</v>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>24.870466321243523</v>
       </c>
       <c r="N3" s="4">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>3.1168831168831175</v>
-      </c>
-      <c r="O3" s="7">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
-        <v>34.570933976335134</v>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>6.296320587656588</v>
+      </c>
+      <c r="O3" s="4">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>71.567956744279726</v>
       </c>
       <c r="P3" s="5">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
-        <v>0.48898067859031302</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <v>1.0122766159021177</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="S3" s="18">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B4" s="7">
         <v>69.599999999999994</v>
       </c>
       <c r="C4" s="3">
-        <v>2.0499999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="D4" s="4">
-        <v>10000</v>
+        <f>6010*2</f>
+        <v>12020</v>
       </c>
       <c r="E4" s="7">
-        <v>113</v>
+        <v>150</v>
       </c>
       <c r="F4" s="3">
         <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
-        <v>11.237946447213039</v>
+        <v>9.2652804849046397</v>
       </c>
       <c r="G4" s="4">
         <f>12/Table6[[#This Row],[Opór uzwojeń '[U/1A']]]</f>
-        <v>5.8536585365853666</v>
+        <v>5.333333333333333</v>
       </c>
       <c r="H4" s="5">
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
-        <v>65.783101154417793</v>
+        <v>49.414829252824745</v>
       </c>
       <c r="I4" s="3">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>24</v>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>3005</v>
       </c>
       <c r="J4" s="4">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>11.707317073170733</v>
-      </c>
-      <c r="K4" s="4">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>131.56620230883559</v>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>2.6666666666666665</v>
+      </c>
+      <c r="K4" s="7">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <v>24.707414626412373</v>
       </c>
       <c r="L4" s="5">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>1.8903189986901665</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>0.35499158945994791</v>
       </c>
       <c r="M4" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>5000</v>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>19.966722129783694</v>
       </c>
       <c r="N4" s="4">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>5.8536585365853666</v>
-      </c>
-      <c r="O4" s="7">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
-        <v>65.783101154417793</v>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>8.8740987243483076</v>
+      </c>
+      <c r="O4" s="4">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>82.221013731821543</v>
       </c>
       <c r="P4" s="5">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
-        <v>0.94515949934508325</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <v>1.1813364041928383</v>
       </c>
       <c r="R4" s="14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="S4" s="17">
         <v>30</v>
@@ -1539,7 +1499,7 @@
     </row>
     <row r="5" spans="1:19" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5" s="7">
         <v>71.8</v>
@@ -1548,14 +1508,16 @@
         <v>2.5</v>
       </c>
       <c r="D5" s="4">
-        <v>10000</v>
+        <f>5325*2</f>
+        <v>10650</v>
       </c>
       <c r="E5" s="7">
-        <v>123</v>
+        <f>280/2</f>
+        <v>140</v>
       </c>
       <c r="F5" s="3">
         <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
-        <v>11.165515032611918</v>
+        <v>10.445944152228623</v>
       </c>
       <c r="G5" s="4">
         <f>12/Table6[[#This Row],[Opór uzwojeń '[U/1A']]]</f>
@@ -1563,42 +1525,42 @@
       </c>
       <c r="H5" s="5">
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
-        <v>53.594472156537201</v>
+        <v>50.140531930697392</v>
       </c>
       <c r="I5" s="3">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>24</v>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>2662.5</v>
       </c>
       <c r="J5" s="4">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>9.6</v>
-      </c>
-      <c r="K5" s="4">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>107.1889443130744</v>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>2.4</v>
+      </c>
+      <c r="K5" s="7">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <v>25.070265965348696</v>
       </c>
       <c r="L5" s="5">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>1.4928822327726241</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>0.34916804965666709</v>
       </c>
       <c r="M5" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>5000</v>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>22.535211267605632</v>
       </c>
       <c r="N5" s="4">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>4.8</v>
-      </c>
-      <c r="O5" s="7">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
-        <v>53.594472156537201</v>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>9.0140845070422522</v>
+      </c>
+      <c r="O5" s="4">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>94.160623344032658</v>
       </c>
       <c r="P5" s="5">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
-        <v>0.74644111638631205</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <v>1.3114292944851345</v>
       </c>
       <c r="R5" s="15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S5" s="16">
         <v>7.5</v>
@@ -1606,66 +1568,67 @@
     </row>
     <row r="6" spans="1:19" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6" s="7">
         <v>75.5</v>
       </c>
       <c r="C6" s="3">
-        <v>3.86</v>
+        <v>3.8</v>
       </c>
       <c r="D6" s="4">
-        <v>10000</v>
+        <v>9300</v>
       </c>
       <c r="E6" s="7">
-        <v>110</v>
+        <f>210/2</f>
+        <v>105</v>
       </c>
       <c r="F6" s="3">
         <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
-        <v>11.053692769595553</v>
+        <v>11.91197738586502</v>
       </c>
       <c r="G6" s="4">
         <f>12/Table6[[#This Row],[Opór uzwojeń '[U/1A']]]</f>
-        <v>3.1088082901554404</v>
+        <v>3.1578947368421053</v>
       </c>
       <c r="H6" s="5">
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
-        <v>34.363811718949904</v>
+        <v>37.616770692205328</v>
       </c>
       <c r="I6" s="3">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>24</v>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>2325</v>
       </c>
       <c r="J6" s="4">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>6.2176165803108807</v>
-      </c>
-      <c r="K6" s="4">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>68.727623437899808</v>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>1.5789473684210524</v>
+      </c>
+      <c r="K6" s="7">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <v>18.808385346102664</v>
       </c>
       <c r="L6" s="5">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>0.91029964818410347</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>0.24911768670334655</v>
       </c>
       <c r="M6" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>5000</v>
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>25.806451612903224</v>
       </c>
       <c r="N6" s="4">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>3.1088082901554404</v>
-      </c>
-      <c r="O6" s="7">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
-        <v>34.363811718949904</v>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>6.7911714770797964</v>
+      </c>
+      <c r="O6" s="4">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>80.896281058506077</v>
       </c>
       <c r="P6" s="5">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
-        <v>0.45514982409205174</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <v>1.0714739213047162</v>
       </c>
       <c r="R6" s="15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="S6" s="16">
         <f>S2*S4*PI()/(S5*60000)</f>
@@ -1674,7 +1637,7 @@
     </row>
     <row r="7" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B7" s="7">
         <v>54</v>
@@ -1701,97 +1664,82 @@
         <v>44.346933343125713</v>
       </c>
       <c r="I7" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>5000</v>
+      </c>
+      <c r="J7" s="4">
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>4</v>
+      </c>
+      <c r="K7" s="7">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <v>22.173466671562853</v>
+      </c>
+      <c r="L7" s="5">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>0.41061975317708987</v>
+      </c>
+      <c r="M7" s="3">
         <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
         <v>12</v>
       </c>
-      <c r="J7" s="4">
+      <c r="N7" s="4">
         <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>8</v>
       </c>
-      <c r="K7" s="4">
+      <c r="O7" s="4">
         <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>44.346933343125706</v>
       </c>
-      <c r="L7" s="5">
+      <c r="P7" s="5">
         <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>0.82123950635417975</v>
       </c>
-      <c r="M7" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>10000</v>
-      </c>
-      <c r="N7" s="4">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>8</v>
-      </c>
-      <c r="O7" s="7">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
-        <v>44.346933343125706</v>
-      </c>
-      <c r="P7" s="5">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
-        <v>0.82123950635417975</v>
-      </c>
     </row>
     <row r="8" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8" s="7">
-        <v>109.5</v>
-      </c>
-      <c r="C8" s="3">
-        <v>3.2</v>
-      </c>
-      <c r="D8" s="4">
-        <v>10000</v>
-      </c>
-      <c r="E8" s="7">
-        <v>200</v>
-      </c>
-      <c r="F8" s="3">
-        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
-        <v>10.848000921143585</v>
-      </c>
-      <c r="G8" s="4">
-        <f>12/Table6[[#This Row],[Opór uzwojeń '[U/1A']]]</f>
-        <v>3.75</v>
-      </c>
-      <c r="H8" s="5">
-        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
-        <v>40.680003454288446</v>
+      <c r="F8" s="3" t="e">
+        <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G8" s="4" t="e">
+        <f>12/Table6[[#This Row],[Opór uzwojeń '[U/1A']]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H8" s="5" t="e">
+        <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="I8" s="3">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>24</v>
-      </c>
-      <c r="J8" s="4">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>7.5</v>
-      </c>
-      <c r="K8" s="4">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>81.360006908576892</v>
-      </c>
-      <c r="L8" s="5">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>0.74301376172216338</v>
-      </c>
-      <c r="M8" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>5000</v>
-      </c>
-      <c r="N8" s="4">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>3.75</v>
-      </c>
-      <c r="O8" s="7">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
-        <v>40.680003454288446</v>
-      </c>
-      <c r="P8" s="5">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
-        <v>0.37150688086108169</v>
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
+      </c>
+      <c r="J8" s="4" t="e">
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K8" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L8" s="5" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M8" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N8" s="4" t="e">
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O8" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="P8" s="5" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="9" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -1807,36 +1755,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I9" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I9" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J9" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K9" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K9" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L9" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M9" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M9" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N9" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O9" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O9" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P9" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -1853,36 +1801,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I10" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I10" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J10" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K10" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K10" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L10" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M10" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M10" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N10" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O10" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O10" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P10" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Q10" s="13"/>
@@ -1900,36 +1848,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I11" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I11" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J11" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K11" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K11" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L11" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M11" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M11" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N11" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O11" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O11" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P11" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -1946,36 +1894,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I12" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I12" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J12" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K12" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K12" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L12" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M12" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M12" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N12" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O12" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O12" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P12" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -1992,36 +1940,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I13" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I13" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J13" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K13" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K13" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L13" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M13" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M13" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N13" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O13" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O13" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P13" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2038,36 +1986,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I14" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I14" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J14" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K14" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K14" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L14" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M14" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M14" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N14" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O14" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O14" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P14" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2084,36 +2032,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I15" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I15" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J15" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K15" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K15" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L15" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M15" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M15" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N15" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O15" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O15" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P15" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2130,36 +2078,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I16" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I16" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J16" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K16" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K16" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L16" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M16" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M16" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N16" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O16" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O16" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P16" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2176,36 +2124,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I17" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I17" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J17" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K17" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K17" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L17" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M17" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M17" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N17" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O17" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O17" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P17" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2222,36 +2170,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I18" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I18" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J18" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K18" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K18" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L18" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M18" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M18" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N18" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O18" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O18" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P18" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2268,36 +2216,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I19" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I19" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J19" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K19" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K19" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L19" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M19" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M19" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N19" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O19" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O19" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P19" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2314,36 +2262,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I20" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I20" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J20" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K20" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K20" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L20" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M20" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M20" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N20" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O20" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O20" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P20" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2360,36 +2308,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I21" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I21" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J21" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K21" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K21" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L21" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M21" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M21" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N21" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O21" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O21" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P21" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2406,36 +2354,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I22" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I22" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J22" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K22" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K22" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L22" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M22" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M22" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N22" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O22" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O22" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P22" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2452,36 +2400,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I23" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I23" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J23" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K23" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K23" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L23" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M23" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M23" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N23" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O23" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O23" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P23" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2498,36 +2446,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I24" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I24" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J24" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K24" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K24" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L24" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M24" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M24" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N24" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O24" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O24" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P24" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2544,36 +2492,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I25" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I25" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J25" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K25" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K25" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L25" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M25" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M25" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N25" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O25" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O25" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P25" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2590,36 +2538,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I26" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I26" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J26" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K26" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K26" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L26" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M26" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M26" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N26" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O26" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O26" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P26" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2636,36 +2584,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I27" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I27" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J27" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K27" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K27" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L27" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M27" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M27" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N27" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O27" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O27" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P27" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2682,36 +2630,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I28" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I28" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J28" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K28" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K28" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L28" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M28" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M28" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N28" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O28" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O28" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P28" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2728,36 +2676,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I29" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I29" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J29" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K29" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K29" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L29" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M29" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M29" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N29" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O29" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O29" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P29" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2774,36 +2722,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I30" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I30" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J30" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K30" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K30" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L30" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M30" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M30" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N30" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O30" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O30" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P30" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2820,36 +2768,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I31" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I31" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J31" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K31" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K31" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L31" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M31" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M31" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N31" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O31" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O31" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P31" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2866,36 +2814,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I32" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I32" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J32" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K32" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K32" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L32" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M32" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M32" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N32" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O32" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O32" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P32" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2912,36 +2860,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I33" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I33" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J33" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K33" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K33" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L33" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M33" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M33" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N33" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O33" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O33" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P33" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2958,36 +2906,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I34" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I34" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J34" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K34" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K34" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L34" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M34" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M34" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N34" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O34" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O34" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P34" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3004,36 +2952,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I35" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I35" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J35" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K35" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K35" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L35" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M35" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M35" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N35" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O35" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O35" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P35" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3050,36 +2998,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I36" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I36" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J36" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K36" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K36" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L36" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M36" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M36" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N36" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O36" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O36" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P36" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3096,36 +3044,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I37" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I37" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J37" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K37" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K37" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L37" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M37" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M37" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N37" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O37" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O37" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P37" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3142,36 +3090,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I38" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I38" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J38" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K38" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K38" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L38" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M38" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M38" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N38" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O38" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O38" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P38" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3188,36 +3136,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I39" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I39" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J39" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K39" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K39" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L39" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M39" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M39" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N39" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O39" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O39" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P39" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3234,36 +3182,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I40" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I40" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J40" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K40" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K40" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L40" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M40" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M40" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N40" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O40" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O40" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P40" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3280,36 +3228,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I41" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I41" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J41" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K41" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K41" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L41" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M41" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M41" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N41" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O41" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O41" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P41" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3326,36 +3274,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I42" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I42" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J42" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K42" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K42" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L42" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M42" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M42" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N42" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O42" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O42" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P42" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3372,36 +3320,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I43" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I43" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J43" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K43" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K43" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L43" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M43" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M43" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N43" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O43" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O43" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P43" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3418,36 +3366,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I44" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I44" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J44" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K44" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K44" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L44" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M44" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M44" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N44" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O44" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O44" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P44" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3464,36 +3412,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I45" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I45" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J45" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K45" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K45" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L45" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M45" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M45" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N45" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O45" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O45" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P45" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3510,36 +3458,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I46" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I46" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J46" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K46" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K46" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L46" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M46" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M46" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N46" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O46" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O46" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P46" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3556,36 +3504,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I47" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I47" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J47" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K47" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K47" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L47" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M47" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M47" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N47" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O47" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O47" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P47" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3602,36 +3550,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I48" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I48" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J48" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K48" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K48" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L48" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M48" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M48" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N48" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O48" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O48" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P48" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3648,36 +3596,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I49" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I49" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J49" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K49" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K49" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L49" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M49" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M49" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N49" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O49" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O49" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P49" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3694,36 +3642,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I50" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I50" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J50" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K50" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K50" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L50" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M50" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M50" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N50" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O50" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O50" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P50" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3740,36 +3688,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I51" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I51" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J51" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K51" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K51" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L51" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M51" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M51" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N51" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O51" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O51" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P51" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3786,36 +3734,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I52" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I52" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J52" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K52" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K52" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L52" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M52" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M52" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N52" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O52" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O52" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P52" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3832,36 +3780,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I53" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I53" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J53" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K53" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K53" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L53" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M53" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M53" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N53" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O53" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O53" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P53" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3878,36 +3826,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I54" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I54" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J54" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K54" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K54" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L54" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M54" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M54" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N54" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O54" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O54" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P54" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3924,36 +3872,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I55" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I55" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J55" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K55" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K55" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L55" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M55" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M55" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N55" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O55" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O55" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P55" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -3970,36 +3918,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I56" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I56" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J56" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K56" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K56" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L56" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M56" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M56" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N56" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O56" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O56" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P56" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -4016,36 +3964,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I57" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I57" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J57" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K57" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K57" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L57" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M57" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M57" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N57" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O57" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O57" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P57" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -4062,36 +4010,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I58" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I58" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J58" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K58" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K58" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L58" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M58" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M58" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N58" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O58" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O58" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P58" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -4108,36 +4056,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I59" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I59" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J59" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K59" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K59" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L59" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M59" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M59" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N59" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O59" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O59" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P59" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -4154,36 +4102,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I60" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I60" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J60" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K60" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K60" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L60" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M60" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M60" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N60" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O60" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O60" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P60" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -4200,36 +4148,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I61" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I61" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J61" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K61" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K61" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L61" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M61" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M61" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N61" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O61" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O61" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P61" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -4246,36 +4194,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I62" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I62" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J62" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K62" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K62" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L62" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M62" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M62" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N62" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O62" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O62" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P62" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -4292,36 +4240,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I63" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I63" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J63" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K63" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K63" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L63" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M63" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M63" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N63" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O63" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O63" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P63" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -4338,36 +4286,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I64" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I64" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J64" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K64" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K64" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L64" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M64" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M64" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N64" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O64" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O64" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P64" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -4384,36 +4332,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I65" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I65" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J65" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K65" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K65" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L65" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M65" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M65" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N65" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O65" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O65" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P65" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -4430,36 +4378,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I66" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I66" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J66" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K66" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K66" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L66" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M66" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M66" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N66" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O66" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O66" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P66" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -4476,36 +4424,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I67" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I67" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J67" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K67" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K67" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L67" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M67" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M67" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N67" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O67" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O67" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P67" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -4522,36 +4470,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I68" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I68" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J68" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K68" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K68" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L68" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M68" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M68" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N68" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O68" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O68" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P68" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -4568,36 +4516,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I69" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I69" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J69" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K69" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K69" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L69" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M69" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M69" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N69" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O69" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O69" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P69" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -4614,36 +4562,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I70" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I70" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J70" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K70" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K70" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L70" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M70" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M70" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N70" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O70" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O70" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P70" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -4660,36 +4608,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I71" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I71" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J71" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K71" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K71" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L71" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M71" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M71" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N71" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O71" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O71" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P71" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -4706,36 +4654,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I72" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I72" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J72" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K72" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K72" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L72" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M72" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M72" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N72" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O72" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O72" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P72" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -4752,36 +4700,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I73" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I73" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J73" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K73" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K73" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L73" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M73" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M73" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N73" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O73" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O73" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P73" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -4798,36 +4746,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I74" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I74" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J74" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K74" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K74" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L74" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M74" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M74" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N74" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O74" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O74" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P74" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -4844,36 +4792,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I75" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I75" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J75" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K75" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K75" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L75" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M75" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M75" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N75" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O75" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O75" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P75" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -4890,36 +4838,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I76" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I76" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J76" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K76" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K76" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L76" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M76" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M76" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N76" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O76" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O76" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P76" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -4936,36 +4884,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I77" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I77" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J77" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K77" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K77" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L77" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M77" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M77" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N77" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O77" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O77" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P77" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -4982,36 +4930,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I78" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I78" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J78" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K78" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K78" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L78" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M78" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M78" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N78" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O78" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O78" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P78" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -5028,36 +4976,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I79" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I79" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J79" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K79" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K79" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L79" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M79" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M79" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N79" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O79" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O79" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P79" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -5074,36 +5022,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I80" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I80" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J80" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K80" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K80" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L80" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M80" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M80" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N80" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O80" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O80" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P80" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -5120,36 +5068,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I81" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I81" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J81" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K81" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K81" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L81" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M81" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M81" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N81" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O81" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O81" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P81" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -5166,36 +5114,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I82" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I82" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J82" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K82" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K82" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L82" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M82" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M82" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N82" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O82" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O82" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P82" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -5212,36 +5160,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I83" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I83" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J83" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K83" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K83" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L83" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M83" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M83" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N83" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O83" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O83" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P83" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -5258,36 +5206,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I84" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I84" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J84" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K84" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K84" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L84" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M84" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M84" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N84" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O84" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O84" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P84" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -5304,36 +5252,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I85" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I85" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J85" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K85" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K85" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L85" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M85" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M85" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N85" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O85" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O85" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P85" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -5350,36 +5298,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I86" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I86" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J86" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K86" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K86" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L86" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M86" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M86" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N86" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O86" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O86" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P86" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -5396,36 +5344,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I87" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I87" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J87" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K87" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K87" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L87" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M87" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M87" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N87" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O87" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O87" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P87" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -5442,36 +5390,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I88" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I88" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J88" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K88" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K88" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L88" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M88" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M88" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N88" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O88" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O88" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P88" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -5488,36 +5436,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I89" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I89" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J89" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K89" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K89" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L89" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M89" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M89" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N89" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O89" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O89" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P89" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -5534,36 +5482,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I90" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I90" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J90" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K90" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K90" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L90" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M90" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M90" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N90" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O90" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O90" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P90" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -5580,36 +5528,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I91" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I91" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J91" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K91" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K91" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L91" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M91" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M91" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N91" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O91" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O91" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P91" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -5626,36 +5574,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I92" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I92" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J92" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K92" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K92" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L92" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M92" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M92" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N92" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O92" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O92" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P92" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -5672,36 +5620,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I93" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I93" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J93" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K93" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K93" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L93" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M93" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M93" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N93" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O93" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O93" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P93" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -5718,36 +5666,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I94" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I94" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J94" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K94" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K94" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L94" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M94" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M94" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N94" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O94" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O94" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P94" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -5764,36 +5712,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I95" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I95" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J95" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K95" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K95" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L95" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M95" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M95" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N95" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O95" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O95" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P95" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -5810,36 +5758,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I96" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I96" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J96" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K96" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K96" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L96" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M96" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M96" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N96" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O96" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O96" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P96" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -5856,36 +5804,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I97" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I97" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J97" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K97" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K97" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L97" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M97" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M97" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N97" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O97" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O97" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P97" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -5902,36 +5850,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I98" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I98" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J98" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K98" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K98" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L98" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M98" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M98" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N98" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O98" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O98" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P98" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -5948,36 +5896,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I99" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I99" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J99" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K99" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K99" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L99" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M99" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M99" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N99" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O99" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O99" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P99" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -5994,36 +5942,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I100" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I100" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J100" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K100" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K100" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L100" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M100" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M100" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N100" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O100" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O100" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P100" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -6040,36 +5988,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I101" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I101" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J101" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K101" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K101" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L101" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M101" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M101" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N101" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O101" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O101" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P101" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -6086,36 +6034,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I102" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I102" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J102" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K102" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K102" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L102" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M102" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M102" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N102" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O102" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O102" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P102" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -6132,36 +6080,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I103" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I103" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J103" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K103" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K103" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L103" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M103" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M103" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N103" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O103" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O103" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P103" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -6178,36 +6126,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I104" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I104" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J104" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K104" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K104" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L104" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M104" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M104" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N104" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O104" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O104" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P104" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -6224,36 +6172,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I105" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I105" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J105" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K105" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K105" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L105" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M105" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M105" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N105" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O105" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O105" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P105" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -6270,36 +6218,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I106" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I106" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J106" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K106" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K106" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L106" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M106" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M106" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N106" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O106" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O106" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P106" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -6316,36 +6264,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I107" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I107" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J107" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K107" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K107" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L107" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M107" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M107" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N107" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O107" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O107" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P107" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -6362,36 +6310,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I108" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I108" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J108" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K108" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K108" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L108" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M108" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M108" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N108" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O108" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O108" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P108" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -6408,36 +6356,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I109" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I109" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J109" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K109" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K109" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L109" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M109" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M109" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N109" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O109" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O109" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P109" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -6454,36 +6402,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I110" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I110" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J110" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K110" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K110" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L110" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M110" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M110" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N110" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O110" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O110" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P110" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -6500,36 +6448,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I111" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I111" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J111" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K111" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K111" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L111" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M111" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M111" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N111" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O111" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O111" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P111" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -6546,36 +6494,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I112" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I112" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J112" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K112" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K112" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L112" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M112" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M112" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N112" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O112" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O112" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P112" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -6592,36 +6540,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I113" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I113" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J113" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K113" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K113" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L113" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M113" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M113" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N113" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O113" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O113" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P113" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -6638,36 +6586,36 @@
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I114" s="3" t="e">
-        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>#DIV/0!</v>
+      <c r="I114" s="3">
+        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
+        <v>0</v>
       </c>
       <c r="J114" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K114" s="4" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K114" s="7" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L114" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M114" s="3">
-        <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>0</v>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M114" s="3" t="e">
+        <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="N114" s="4" t="e">
-        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O114" s="7" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
+        <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O114" s="4" t="e">
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
         <v>#DIV/0!</v>
       </c>
       <c r="P114" s="5" t="e">
-        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
+        <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -6675,12 +6623,12 @@
   <mergeCells count="1">
     <mergeCell ref="R1:S1"/>
   </mergeCells>
-  <conditionalFormatting sqref="A1:P2 A3:E6 I3:P6 F3:G114 H3:H115">
-    <cfRule type="expression" dxfId="1" priority="1">
+  <conditionalFormatting sqref="I1:P6 A3:E6 F3:G114 H3:H115">
+    <cfRule type="expression" dxfId="1" priority="5">
+      <formula>$O1=_xlfn.AGGREGATE(4,6,$O:$O)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="0" priority="6">
       <formula>$K1=_xlfn.AGGREGATE(4,6,$K:$K)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="0" priority="4">
-      <formula>$O1=_xlfn.AGGREGATE(4,6,$O:$O)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/SilniczkiExcel.xlsx
+++ b/SilniczkiExcel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\tech\robotyka\robots\evangelion-turbo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E2355DB-D683-4D55-A9AD-EBBE2B44594A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2DC4335-43C8-4DFE-BBEE-2DCE54F300C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="3300" windowWidth="29040" windowHeight="15840" xr2:uid="{511008C5-3BC9-4B59-854A-53C66BDAD283}"/>
   </bookViews>
@@ -1303,63 +1303,63 @@
         <v>75.3</v>
       </c>
       <c r="C2" s="3">
-        <v>2.35</v>
+        <v>2.54</v>
       </c>
       <c r="D2" s="4">
-        <v>11900</v>
+        <v>11200</v>
       </c>
       <c r="E2" s="7">
         <v>160</v>
       </c>
       <c r="F2" s="3">
         <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
-        <v>9.3278171016816369</v>
+        <v>9.8848861512332036</v>
       </c>
       <c r="G2" s="4">
         <f>12/Table6[[#This Row],[Opór uzwojeń '[U/1A']]]</f>
-        <v>5.1063829787234036</v>
+        <v>4.7244094488188972</v>
       </c>
       <c r="H2" s="5">
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
-        <v>47.631406476672183</v>
+        <v>46.700249533385211</v>
       </c>
       <c r="I2" s="3">
         <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>2975</v>
+        <v>5600</v>
       </c>
       <c r="J2" s="4">
         <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>2.5531914893617018</v>
+        <v>4.7244094488188972</v>
       </c>
       <c r="K2" s="7">
         <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
-        <v>23.815703238336095</v>
+        <v>46.700249533385211</v>
       </c>
       <c r="L2" s="5">
         <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
-        <v>0.31627759944669448</v>
+        <v>0.62018923683114491</v>
       </c>
       <c r="M2" s="3">
         <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>20.168067226890756</v>
+        <v>23.571428571428573</v>
       </c>
       <c r="N2" s="4">
         <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>8.5821562667620217</v>
+        <v>9.2800899887514063</v>
       </c>
       <c r="O2" s="4">
         <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>80.052783994407022</v>
+        <v>91.732633012006673</v>
       </c>
       <c r="P2" s="5">
         <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>1.0631179813334266</v>
+        <v>1.2182288580611775</v>
       </c>
       <c r="R2" s="14" t="s">
         <v>6</v>
       </c>
       <c r="S2" s="17">
-        <v>10000</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="3" spans="1:19" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -1392,41 +1392,41 @@
       </c>
       <c r="I3" s="3">
         <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>2412.5</v>
+        <v>4825</v>
       </c>
       <c r="J3" s="4">
         <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>1.5189873417721518</v>
+        <v>3.0379746835443036</v>
       </c>
       <c r="K3" s="7">
         <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
-        <v>17.265769564557484</v>
+        <v>34.531539129114968</v>
       </c>
       <c r="L3" s="5">
         <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
-        <v>0.2442117335863859</v>
+        <v>0.4884234671727718</v>
       </c>
       <c r="M3" s="3">
         <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>24.870466321243523</v>
+        <v>27.357512953367877</v>
       </c>
       <c r="N3" s="4">
         <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>6.296320587656588</v>
+        <v>6.9259526464222469</v>
       </c>
       <c r="O3" s="4">
         <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>71.567956744279726</v>
+        <v>78.724752418707695</v>
       </c>
       <c r="P3" s="5">
         <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>1.0122766159021177</v>
+        <v>1.1135042774923294</v>
       </c>
       <c r="R3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="S3" s="18">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -1437,58 +1437,57 @@
         <v>69.599999999999994</v>
       </c>
       <c r="C4" s="3">
-        <v>2.25</v>
+        <v>2.42</v>
       </c>
       <c r="D4" s="4">
-        <f>6010*2</f>
-        <v>12020</v>
+        <v>12300</v>
       </c>
       <c r="E4" s="7">
         <v>150</v>
       </c>
       <c r="F4" s="3">
         <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
-        <v>9.2652804849046397</v>
+        <v>9.0345662085872505</v>
       </c>
       <c r="G4" s="4">
         <f>12/Table6[[#This Row],[Opór uzwojeń '[U/1A']]]</f>
-        <v>5.333333333333333</v>
+        <v>4.9586776859504136</v>
       </c>
       <c r="H4" s="5">
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
-        <v>49.414829252824745</v>
+        <v>44.799501860763229</v>
       </c>
       <c r="I4" s="3">
         <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>3005</v>
+        <v>6150</v>
       </c>
       <c r="J4" s="4">
         <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>2.6666666666666665</v>
+        <v>4.9586776859504136</v>
       </c>
       <c r="K4" s="7">
         <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
-        <v>24.707414626412373</v>
+        <v>44.799501860763229</v>
       </c>
       <c r="L4" s="5">
         <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
-        <v>0.35499158945994791</v>
+        <v>0.64367100374659814</v>
       </c>
       <c r="M4" s="3">
         <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>19.966722129783694</v>
+        <v>21.463414634146343</v>
       </c>
       <c r="N4" s="4">
         <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>8.8740987243483076</v>
+        <v>8.8691796008869197</v>
       </c>
       <c r="O4" s="4">
         <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>82.221013731821543</v>
+        <v>80.129190320064325</v>
       </c>
       <c r="P4" s="5">
         <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>1.1813364041928383</v>
+        <v>1.1512814701158669</v>
       </c>
       <c r="R4" s="14" t="s">
         <v>18</v>
@@ -1505,7 +1504,8 @@
         <v>71.8</v>
       </c>
       <c r="C5" s="3">
-        <v>2.5</v>
+        <f>1.32*2</f>
+        <v>2.64</v>
       </c>
       <c r="D5" s="4">
         <f>5325*2</f>
@@ -1517,47 +1517,47 @@
       </c>
       <c r="F5" s="3">
         <f>(12-(Table6[[#This Row],[Prąd 12V '[mA']]]/1000)*Table6[[#This Row],[Opór uzwojeń '[U/1A']]])/(Table6[[#This Row],[RPM 12V]]*PI()/30)*1000</f>
-        <v>10.445944152228623</v>
+        <v>10.428369859921013</v>
       </c>
       <c r="G5" s="4">
         <f>12/Table6[[#This Row],[Opór uzwojeń '[U/1A']]]</f>
-        <v>4.8</v>
+        <v>4.545454545454545</v>
       </c>
       <c r="H5" s="5">
         <f>(Table6[[#This Row],[Stała momentu '[mNm/A']]]*Table6[[#This Row],[Prąd w zwarciu 12V '[A']]])</f>
-        <v>50.140531930697392</v>
+        <v>47.401681181459146</v>
       </c>
       <c r="I5" s="3">
         <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>2662.5</v>
+        <v>5325</v>
       </c>
       <c r="J5" s="4">
         <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>2.4</v>
+        <v>4.545454545454545</v>
       </c>
       <c r="K5" s="7">
         <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
-        <v>25.070265965348696</v>
+        <v>47.401681181459146</v>
       </c>
       <c r="L5" s="5">
         <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
-        <v>0.34916804965666709</v>
+        <v>0.66019054570277369</v>
       </c>
       <c r="M5" s="3">
         <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>22.535211267605632</v>
+        <v>24.788732394366196</v>
       </c>
       <c r="N5" s="4">
         <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>9.0140845070422522</v>
+        <v>9.3896713615023462</v>
       </c>
       <c r="O5" s="4">
         <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>94.160623344032658</v>
+        <v>97.918965820854567</v>
       </c>
       <c r="P5" s="5">
         <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>1.3114292944851345</v>
+        <v>1.3637738972263869</v>
       </c>
       <c r="R5" s="15" t="s">
         <v>20</v>
@@ -1597,42 +1597,42 @@
       </c>
       <c r="I6" s="3">
         <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>2325</v>
+        <v>4650</v>
       </c>
       <c r="J6" s="4">
         <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>1.5789473684210524</v>
+        <v>3.1578947368421049</v>
       </c>
       <c r="K6" s="7">
         <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
-        <v>18.808385346102664</v>
+        <v>37.616770692205328</v>
       </c>
       <c r="L6" s="5">
         <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
-        <v>0.24911768670334655</v>
+        <v>0.49823537340669311</v>
       </c>
       <c r="M6" s="3">
         <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>25.806451612903224</v>
+        <v>28.387096774193548</v>
       </c>
       <c r="N6" s="4">
         <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>6.7911714770797964</v>
+        <v>7.4702886247877762</v>
       </c>
       <c r="O6" s="4">
         <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>80.896281058506077</v>
+        <v>88.985909164356698</v>
       </c>
       <c r="P6" s="5">
         <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>1.0714739213047162</v>
+        <v>1.1786213134351882</v>
       </c>
       <c r="R6" s="15" t="s">
         <v>19</v>
       </c>
       <c r="S6" s="16">
         <f>S2*S4*PI()/(S5*60000)</f>
-        <v>2.0943951023931953</v>
+        <v>2.3038346126325151</v>
       </c>
     </row>
     <row r="7" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -1665,35 +1665,35 @@
       </c>
       <c r="I7" s="3">
         <f>Table6[[#This Row],[RPM 12V]]*$S$3/24</f>
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="J7" s="4">
         <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*$S$3/12</f>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K7" s="7">
         <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12</f>
-        <v>22.173466671562853</v>
+        <v>44.346933343125706</v>
       </c>
       <c r="L7" s="5">
         <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*$S$3/12/Table6[[#This Row],[Waga]]</f>
-        <v>0.41061975317708987</v>
+        <v>0.82123950635417975</v>
       </c>
       <c r="M7" s="3">
         <f>$S$2*24/Table6[[#This Row],[RPM 12V]]</f>
-        <v>12</v>
+        <v>13.2</v>
       </c>
       <c r="N7" s="4">
         <f>Table6[[#This Row],[Prąd w zwarciu 12V '[A']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>8</v>
+        <v>8.7999999999999989</v>
       </c>
       <c r="O7" s="4">
         <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12</f>
-        <v>44.346933343125706</v>
+        <v>48.781626677438283</v>
       </c>
       <c r="P7" s="5">
         <f>Table6[[#This Row],[Moment w zwarciu 12V '[mNm']]]*Table6[[#This Row],[Napięcie (Dane RPM)]]/12/Table6[[#This Row],[Waga]]</f>
-        <v>0.82123950635417975</v>
+        <v>0.90336345698959786</v>
       </c>
     </row>
     <row r="8" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
